--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121410858</v>
+        <v>121411500</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680820</v>
+        <v>680512</v>
       </c>
       <c r="R14" t="n">
-        <v>6601031</v>
+        <v>6601083</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121411500</v>
+        <v>121410858</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680512</v>
+        <v>680820</v>
       </c>
       <c r="R15" t="n">
-        <v>6601083</v>
+        <v>6601031</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121411629</v>
+        <v>121410676</v>
       </c>
       <c r="B23" t="n">
-        <v>95667</v>
+        <v>5169</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,34 +2949,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680467</v>
+        <v>680680</v>
       </c>
       <c r="R23" t="n">
-        <v>6601101</v>
+        <v>6601025</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121410676</v>
+        <v>121412756</v>
       </c>
       <c r="B24" t="n">
-        <v>5169</v>
+        <v>57720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,39 +3056,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680680</v>
+        <v>680420</v>
       </c>
       <c r="R24" t="n">
-        <v>6601025</v>
+        <v>6601183</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121412756</v>
+        <v>121412770</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>8421</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3158,29 +3166,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3190,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680420</v>
+        <v>680419</v>
       </c>
       <c r="R25" t="n">
-        <v>6601183</v>
+        <v>6601182</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,6 +3243,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3252,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121412770</v>
+        <v>121410856</v>
       </c>
       <c r="B26" t="n">
-        <v>8421</v>
+        <v>5169</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3268,43 +3278,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680419</v>
+        <v>680820</v>
       </c>
       <c r="R26" t="n">
-        <v>6601182</v>
+        <v>6601031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,7 +3351,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3364,7 +3369,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121410856</v>
+        <v>121412678</v>
       </c>
       <c r="B27" t="n">
         <v>5169</v>
@@ -3409,10 +3414,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680820</v>
+        <v>680425</v>
       </c>
       <c r="R27" t="n">
-        <v>6601031</v>
+        <v>6601193</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121412678</v>
+        <v>121412634</v>
       </c>
       <c r="B28" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3487,21 +3492,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3516,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680425</v>
+        <v>680449</v>
       </c>
       <c r="R28" t="n">
-        <v>6601193</v>
+        <v>6601206</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121412634</v>
+        <v>121413892</v>
       </c>
       <c r="B29" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3590,20 +3595,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3612,21 +3617,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680449</v>
+        <v>680392</v>
       </c>
       <c r="R29" t="n">
-        <v>6601206</v>
+        <v>6601145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,10 +3693,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121413892</v>
+        <v>121410851</v>
       </c>
       <c r="B30" t="n">
-        <v>57367</v>
+        <v>90697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3701,42 +3709,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680392</v>
+        <v>680816</v>
       </c>
       <c r="R30" t="n">
-        <v>6601145</v>
+        <v>6601025</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121410851</v>
+        <v>121412680</v>
       </c>
       <c r="B31" t="n">
-        <v>90697</v>
+        <v>95667</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3807,38 +3807,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680816</v>
+        <v>680489</v>
       </c>
       <c r="R31" t="n">
-        <v>6601025</v>
+        <v>6601147</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,9 +3868,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,22 +3895,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121412680</v>
+        <v>121413970</v>
       </c>
       <c r="B32" t="n">
-        <v>95667</v>
+        <v>5169</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3913,34 +3923,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680489</v>
+        <v>680380</v>
       </c>
       <c r="R32" t="n">
-        <v>6601147</v>
+        <v>6601066</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3970,49 +3989,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121413970</v>
+        <v>121414014</v>
       </c>
       <c r="B33" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4021,34 +4031,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4058,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680380</v>
+        <v>680401</v>
       </c>
       <c r="R33" t="n">
-        <v>6601066</v>
+        <v>6601033</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4102,7 +4111,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4121,7 +4129,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121414014</v>
+        <v>121411092</v>
       </c>
       <c r="B34" t="n">
         <v>57367</v>
@@ -4155,24 +4163,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680401</v>
+        <v>680739</v>
       </c>
       <c r="R34" t="n">
-        <v>6601033</v>
+        <v>6601133</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4231,55 +4236,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121411092</v>
+        <v>121411629</v>
       </c>
       <c r="B35" t="n">
-        <v>57367</v>
+        <v>95667</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680739</v>
+        <v>680467</v>
       </c>
       <c r="R35" t="n">
-        <v>6601133</v>
+        <v>6601101</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121411191</v>
+        <v>121413923</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,21 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680709</v>
+        <v>680385</v>
       </c>
       <c r="R2" t="n">
-        <v>6601109</v>
+        <v>6601107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121411550</v>
+        <v>121411085</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +801,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680577</v>
+        <v>680741</v>
       </c>
       <c r="R3" t="n">
-        <v>6601111</v>
+        <v>6601120</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,19 +866,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,12 +883,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1004,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121414116</v>
+        <v>121411444</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680468</v>
+        <v>680555</v>
       </c>
       <c r="R5" t="n">
-        <v>6601091</v>
+        <v>6601110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121412820</v>
+        <v>121411550</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,42 +1128,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680357</v>
+        <v>680577</v>
       </c>
       <c r="R6" t="n">
-        <v>6601265</v>
+        <v>6601111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,9 +1185,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,22 +1212,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121411439</v>
+        <v>121411500</v>
       </c>
       <c r="B7" t="n">
-        <v>8421</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680555</v>
+        <v>680512</v>
       </c>
       <c r="R7" t="n">
-        <v>6601112</v>
+        <v>6601083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121412711</v>
+        <v>121412634</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>5189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,46 +1343,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680420</v>
+        <v>680449</v>
       </c>
       <c r="R8" t="n">
-        <v>6601183</v>
+        <v>6601206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414121</v>
+        <v>121413970</v>
       </c>
       <c r="B9" t="n">
         <v>5169</v>
@@ -1482,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680458</v>
+        <v>680380</v>
       </c>
       <c r="R9" t="n">
-        <v>6601079</v>
+        <v>6601066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1550,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121412576</v>
+        <v>121412767</v>
       </c>
       <c r="B10" t="n">
         <v>57367</v>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680490</v>
+        <v>680411</v>
       </c>
       <c r="R10" t="n">
-        <v>6601144</v>
+        <v>6601181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121412758</v>
+        <v>121414121</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,21 +1676,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1704,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680420</v>
+        <v>680458</v>
       </c>
       <c r="R11" t="n">
-        <v>6601183</v>
+        <v>6601079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,10 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121413923</v>
+        <v>121411092</v>
       </c>
       <c r="B12" t="n">
-        <v>57242</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,16 +1788,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1801,24 +1806,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680385</v>
+        <v>680739</v>
       </c>
       <c r="R12" t="n">
-        <v>6601107</v>
+        <v>6601133</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1879,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121412669</v>
+        <v>121412680</v>
       </c>
       <c r="B13" t="n">
         <v>95667</v>
@@ -1913,14 +1915,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680434</v>
+        <v>680489</v>
       </c>
       <c r="R13" t="n">
-        <v>6601196</v>
+        <v>6601147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,9 +1952,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,22 +1979,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121411500</v>
+        <v>121410858</v>
       </c>
       <c r="B14" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +2007,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2036,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680512</v>
+        <v>680820</v>
       </c>
       <c r="R14" t="n">
-        <v>6601083</v>
+        <v>6601031</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121410858</v>
+        <v>121411191</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,20 +2110,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2122,7 +2134,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2131,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680820</v>
+        <v>680709</v>
       </c>
       <c r="R15" t="n">
-        <v>6601031</v>
+        <v>6601109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121411749</v>
+        <v>121414116</v>
       </c>
       <c r="B16" t="n">
-        <v>8421</v>
+        <v>90697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,43 +2217,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680501</v>
+        <v>680468</v>
       </c>
       <c r="R16" t="n">
-        <v>6601197</v>
+        <v>6601091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121412767</v>
+        <v>121411749</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>8421</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,46 +2319,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680411</v>
+        <v>680501</v>
       </c>
       <c r="R17" t="n">
-        <v>6601181</v>
+        <v>6601197</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121410996</v>
+        <v>121410676</v>
       </c>
       <c r="B18" t="n">
-        <v>100347</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,34 +2430,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680804</v>
+        <v>680680</v>
       </c>
       <c r="R18" t="n">
-        <v>6601124</v>
+        <v>6601025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121414195</v>
+        <v>121412756</v>
       </c>
       <c r="B19" t="n">
-        <v>95667</v>
+        <v>57720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,34 +2537,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680470</v>
+        <v>680420</v>
       </c>
       <c r="R19" t="n">
-        <v>6601110</v>
+        <v>6601183</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121411085</v>
+        <v>121414014</v>
       </c>
       <c r="B20" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2652,7 +2669,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2662,13 +2679,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680741</v>
+        <v>680401</v>
       </c>
       <c r="R20" t="n">
-        <v>6601120</v>
+        <v>6601033</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2724,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121411444</v>
+        <v>121412758</v>
       </c>
       <c r="B21" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,43 +2753,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680555</v>
+        <v>680420</v>
       </c>
       <c r="R21" t="n">
-        <v>6601110</v>
+        <v>6601183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,6 +2834,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2831,10 +2853,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121412572</v>
+        <v>121411439</v>
       </c>
       <c r="B22" t="n">
-        <v>91312</v>
+        <v>8421</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,37 +2869,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680485</v>
+        <v>680555</v>
       </c>
       <c r="R22" t="n">
-        <v>6601135</v>
+        <v>6601112</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2933,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121410676</v>
+        <v>121412678</v>
       </c>
       <c r="B23" t="n">
         <v>5169</v>
@@ -2978,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680680</v>
+        <v>680425</v>
       </c>
       <c r="R23" t="n">
-        <v>6601025</v>
+        <v>6601193</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121412756</v>
+        <v>121413892</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,20 +3079,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3078,7 +3105,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3088,10 +3115,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680420</v>
+        <v>680392</v>
       </c>
       <c r="R24" t="n">
-        <v>6601183</v>
+        <v>6601145</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,10 +3177,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121412770</v>
+        <v>121412820</v>
       </c>
       <c r="B25" t="n">
-        <v>8421</v>
+        <v>57367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3162,34 +3189,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3199,10 +3225,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680419</v>
+        <v>680357</v>
       </c>
       <c r="R25" t="n">
-        <v>6601182</v>
+        <v>6601265</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,7 +3269,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3262,10 +3287,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121410856</v>
+        <v>121410851</v>
       </c>
       <c r="B26" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,43 +3299,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680820</v>
+        <v>680816</v>
       </c>
       <c r="R26" t="n">
-        <v>6601031</v>
+        <v>6601025</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121412678</v>
+        <v>121412711</v>
       </c>
       <c r="B27" t="n">
-        <v>5169</v>
+        <v>57504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3381,43 +3401,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680425</v>
+        <v>680420</v>
       </c>
       <c r="R27" t="n">
-        <v>6601193</v>
+        <v>6601183</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3476,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121412634</v>
+        <v>121412576</v>
       </c>
       <c r="B28" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3488,20 +3511,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3510,21 +3533,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680449</v>
+        <v>680490</v>
       </c>
       <c r="R28" t="n">
-        <v>6601206</v>
+        <v>6601144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121413892</v>
+        <v>121412572</v>
       </c>
       <c r="B29" t="n">
-        <v>57367</v>
+        <v>91312</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,49 +3621,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680392</v>
+        <v>680485</v>
       </c>
       <c r="R29" t="n">
-        <v>6601145</v>
+        <v>6601135</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3693,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121410851</v>
+        <v>121410856</v>
       </c>
       <c r="B30" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3705,38 +3723,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680816</v>
+        <v>680820</v>
       </c>
       <c r="R30" t="n">
-        <v>6601025</v>
+        <v>6601031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3795,10 +3818,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121412680</v>
+        <v>121410996</v>
       </c>
       <c r="B31" t="n">
-        <v>95667</v>
+        <v>100347</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3811,34 +3834,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2590</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680489</v>
+        <v>680804</v>
       </c>
       <c r="R31" t="n">
-        <v>6601147</v>
+        <v>6601124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,19 +3891,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,22 +3908,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121413970</v>
+        <v>121412770</v>
       </c>
       <c r="B32" t="n">
-        <v>5169</v>
+        <v>8421</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3923,21 +3936,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3956,10 +3969,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680380</v>
+        <v>680419</v>
       </c>
       <c r="R32" t="n">
-        <v>6601066</v>
+        <v>6601182</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,10 +4032,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121414014</v>
+        <v>121412669</v>
       </c>
       <c r="B33" t="n">
-        <v>57367</v>
+        <v>95667</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4031,46 +4044,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680401</v>
+        <v>680434</v>
       </c>
       <c r="R33" t="n">
-        <v>6601033</v>
+        <v>6601196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121411092</v>
+        <v>121414195</v>
       </c>
       <c r="B34" t="n">
-        <v>57367</v>
+        <v>95667</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4141,43 +4146,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680739</v>
+        <v>680470</v>
       </c>
       <c r="R34" t="n">
-        <v>6601133</v>
+        <v>6601110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414116</v>
+        <v>121410676</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,38 +2217,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680468</v>
+        <v>680680</v>
       </c>
       <c r="R16" t="n">
-        <v>6601091</v>
+        <v>6601025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121410676</v>
+        <v>121414116</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,43 +2431,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680680</v>
+        <v>680468</v>
       </c>
       <c r="R18" t="n">
-        <v>6601025</v>
+        <v>6601091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121412678</v>
+        <v>121412820</v>
       </c>
       <c r="B23" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2972,43 +2972,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680425</v>
+        <v>680357</v>
       </c>
       <c r="R23" t="n">
-        <v>6601193</v>
+        <v>6601265</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121412820</v>
+        <v>121412678</v>
       </c>
       <c r="B25" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,46 +3192,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680357</v>
+        <v>680425</v>
       </c>
       <c r="R25" t="n">
-        <v>6601265</v>
+        <v>6601193</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121413923</v>
+        <v>121411444</v>
       </c>
       <c r="B2" t="n">
-        <v>57242</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,24 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680385</v>
+        <v>680555</v>
       </c>
       <c r="R2" t="n">
-        <v>6601107</v>
+        <v>6601110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121411085</v>
+        <v>121413912</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +820,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680741</v>
+        <v>680381</v>
       </c>
       <c r="R3" t="n">
-        <v>6601120</v>
+        <v>6601114</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413912</v>
+        <v>121411550</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680381</v>
+        <v>680577</v>
       </c>
       <c r="R4" t="n">
-        <v>6601114</v>
+        <v>6601111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,9 +965,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121411444</v>
+        <v>121411439</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,31 +1016,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1053,7 +1052,7 @@
         <v>680555</v>
       </c>
       <c r="R5" t="n">
-        <v>6601110</v>
+        <v>6601112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121411550</v>
+        <v>121410996</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,38 +1123,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680577</v>
+        <v>680804</v>
       </c>
       <c r="R6" t="n">
-        <v>6601111</v>
+        <v>6601124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,19 +1184,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,22 +1201,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121411500</v>
+        <v>121411085</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,46 +1225,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680512</v>
+        <v>680741</v>
       </c>
       <c r="R7" t="n">
-        <v>6601083</v>
+        <v>6601120</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121412634</v>
+        <v>121411749</v>
       </c>
       <c r="B8" t="n">
-        <v>5189</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1339,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680449</v>
+        <v>680501</v>
       </c>
       <c r="R8" t="n">
-        <v>6601206</v>
+        <v>6601197</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1550,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121412767</v>
+        <v>121412756</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>57720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,20 +1554,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1588,7 +1580,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1598,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680411</v>
+        <v>680420</v>
       </c>
       <c r="R10" t="n">
-        <v>6601181</v>
+        <v>6601183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121414121</v>
+        <v>121411191</v>
       </c>
       <c r="B11" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,47 +1664,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680458</v>
+        <v>680709</v>
       </c>
       <c r="R11" t="n">
-        <v>6601079</v>
+        <v>6601109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1741,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1772,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121411092</v>
+        <v>121412678</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,31 +1771,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1817,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680739</v>
+        <v>680425</v>
       </c>
       <c r="R12" t="n">
-        <v>6601133</v>
+        <v>6601193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121412680</v>
+        <v>121412758</v>
       </c>
       <c r="B13" t="n">
-        <v>95667</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,34 +1882,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680489</v>
+        <v>680420</v>
       </c>
       <c r="R13" t="n">
-        <v>6601147</v>
+        <v>6601183</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,49 +1948,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121410858</v>
+        <v>121410851</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>90709</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2003,43 +1990,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680820</v>
+        <v>680816</v>
       </c>
       <c r="R14" t="n">
-        <v>6601031</v>
+        <v>6601025</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121411191</v>
+        <v>121412680</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>95680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2110,43 +2092,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680709</v>
+        <v>680489</v>
       </c>
       <c r="R15" t="n">
-        <v>6601109</v>
+        <v>6601147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,9 +2153,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,19 +2180,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121410676</v>
+        <v>121414121</v>
       </c>
       <c r="B16" t="n">
         <v>5169</v>
@@ -2239,21 +2226,25 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680680</v>
+        <v>680458</v>
       </c>
       <c r="R16" t="n">
-        <v>6601025</v>
+        <v>6601079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,6 +2285,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2312,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121411749</v>
+        <v>121412711</v>
       </c>
       <c r="B17" t="n">
-        <v>8421</v>
+        <v>57504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,43 +2316,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680501</v>
+        <v>680420</v>
       </c>
       <c r="R17" t="n">
-        <v>6601197</v>
+        <v>6601183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121414116</v>
+        <v>121411092</v>
       </c>
       <c r="B18" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,34 +2430,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680468</v>
+        <v>680739</v>
       </c>
       <c r="R18" t="n">
-        <v>6601091</v>
+        <v>6601133</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412756</v>
+        <v>121410676</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>5169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,42 +2537,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680420</v>
+        <v>680680</v>
       </c>
       <c r="R19" t="n">
-        <v>6601183</v>
+        <v>6601025</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121414014</v>
+        <v>121413923</v>
       </c>
       <c r="B20" t="n">
-        <v>57367</v>
+        <v>57242</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,16 +2644,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2669,7 +2666,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2679,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680401</v>
+        <v>680385</v>
       </c>
       <c r="R20" t="n">
-        <v>6601033</v>
+        <v>6601107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2741,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121412758</v>
+        <v>121410856</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,43 +2754,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680420</v>
+        <v>680820</v>
       </c>
       <c r="R21" t="n">
-        <v>6601183</v>
+        <v>6601031</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,7 +2827,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2853,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121411439</v>
+        <v>121412770</v>
       </c>
       <c r="B22" t="n">
         <v>8421</v>
@@ -2887,21 +2879,25 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680555</v>
+        <v>680419</v>
       </c>
       <c r="R22" t="n">
-        <v>6601112</v>
+        <v>6601182</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2942,6 +2938,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2960,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121412820</v>
+        <v>121412572</v>
       </c>
       <c r="B23" t="n">
-        <v>57367</v>
+        <v>91324</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2972,49 +2969,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680357</v>
+        <v>680485</v>
       </c>
       <c r="R23" t="n">
-        <v>6601265</v>
+        <v>6601135</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3070,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121413892</v>
+        <v>121414195</v>
       </c>
       <c r="B24" t="n">
-        <v>57367</v>
+        <v>95680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,46 +3071,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680392</v>
+        <v>680470</v>
       </c>
       <c r="R24" t="n">
-        <v>6601145</v>
+        <v>6601110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121412678</v>
+        <v>121414014</v>
       </c>
       <c r="B25" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,43 +3173,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680425</v>
+        <v>680401</v>
       </c>
       <c r="R25" t="n">
-        <v>6601193</v>
+        <v>6601033</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3287,10 +3271,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121410851</v>
+        <v>121412820</v>
       </c>
       <c r="B26" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3303,34 +3287,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680816</v>
+        <v>680357</v>
       </c>
       <c r="R26" t="n">
-        <v>6601025</v>
+        <v>6601265</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3389,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121412711</v>
+        <v>121413892</v>
       </c>
       <c r="B27" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3405,21 +3397,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,7 +3419,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3437,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680420</v>
+        <v>680392</v>
       </c>
       <c r="R27" t="n">
-        <v>6601183</v>
+        <v>6601145</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3499,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121412576</v>
+        <v>121412634</v>
       </c>
       <c r="B28" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,20 +3503,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3533,24 +3525,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680490</v>
+        <v>680449</v>
       </c>
       <c r="R28" t="n">
-        <v>6601144</v>
+        <v>6601206</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121412572</v>
+        <v>121410858</v>
       </c>
       <c r="B29" t="n">
-        <v>91312</v>
+        <v>5189</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3625,37 +3614,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680485</v>
+        <v>680820</v>
       </c>
       <c r="R29" t="n">
-        <v>6601135</v>
+        <v>6601031</v>
       </c>
       <c r="S29" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3711,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121410856</v>
+        <v>121412576</v>
       </c>
       <c r="B30" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3723,43 +3717,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680820</v>
+        <v>680490</v>
       </c>
       <c r="R30" t="n">
-        <v>6601031</v>
+        <v>6601144</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3818,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121410996</v>
+        <v>121411500</v>
       </c>
       <c r="B31" t="n">
-        <v>100347</v>
+        <v>5169</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3834,34 +3831,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680804</v>
+        <v>680512</v>
       </c>
       <c r="R31" t="n">
-        <v>6601124</v>
+        <v>6601083</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3920,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121412770</v>
+        <v>121414116</v>
       </c>
       <c r="B32" t="n">
-        <v>8421</v>
+        <v>90709</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3932,47 +3934,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680419</v>
+        <v>680468</v>
       </c>
       <c r="R32" t="n">
-        <v>6601182</v>
+        <v>6601091</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,7 +4006,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4035,7 +4027,7 @@
         <v>121412669</v>
       </c>
       <c r="B33" t="n">
-        <v>95667</v>
+        <v>95680</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4134,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121414195</v>
+        <v>121412767</v>
       </c>
       <c r="B34" t="n">
-        <v>95667</v>
+        <v>57367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4146,38 +4138,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680470</v>
+        <v>680411</v>
       </c>
       <c r="R34" t="n">
-        <v>6601110</v>
+        <v>6601181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
         <v>121411629</v>
       </c>
       <c r="B35" t="n">
-        <v>95667</v>
+        <v>95680</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121411444</v>
+        <v>121413892</v>
       </c>
       <c r="B2" t="n">
         <v>57367</v>
@@ -709,21 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680555</v>
+        <v>680392</v>
       </c>
       <c r="R2" t="n">
-        <v>6601110</v>
+        <v>6601145</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121413912</v>
+        <v>121412756</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680381</v>
+        <v>680420</v>
       </c>
       <c r="R3" t="n">
-        <v>6601114</v>
+        <v>6601183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121411550</v>
+        <v>121411749</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>8421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +907,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680577</v>
+        <v>680501</v>
       </c>
       <c r="R4" t="n">
-        <v>6601111</v>
+        <v>6601197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,19 +973,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,22 +990,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121411439</v>
+        <v>121410676</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680555</v>
+        <v>680680</v>
       </c>
       <c r="R5" t="n">
-        <v>6601112</v>
+        <v>6601025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121410996</v>
+        <v>121412678</v>
       </c>
       <c r="B6" t="n">
-        <v>100360</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,34 +1125,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680804</v>
+        <v>680425</v>
       </c>
       <c r="R6" t="n">
-        <v>6601124</v>
+        <v>6601193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121411085</v>
+        <v>121412680</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>95681</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,49 +1228,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680741</v>
+        <v>680489</v>
       </c>
       <c r="R7" t="n">
-        <v>6601120</v>
+        <v>6601147</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,9 +1289,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,22 +1316,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121411749</v>
+        <v>121410858</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>5189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680501</v>
+        <v>680820</v>
       </c>
       <c r="R8" t="n">
-        <v>6601197</v>
+        <v>6601031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121413970</v>
+        <v>121413923</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>57242</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,34 +1447,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1479,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680380</v>
+        <v>680385</v>
       </c>
       <c r="R9" t="n">
-        <v>6601066</v>
+        <v>6601107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1527,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1542,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121412756</v>
+        <v>121410856</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>5169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,42 +1561,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680420</v>
+        <v>680820</v>
       </c>
       <c r="R10" t="n">
-        <v>6601183</v>
+        <v>6601031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411191</v>
+        <v>121411500</v>
       </c>
       <c r="B11" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,31 +1664,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680709</v>
+        <v>680512</v>
       </c>
       <c r="R11" t="n">
-        <v>6601109</v>
+        <v>6601083</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121412678</v>
+        <v>121412758</v>
       </c>
       <c r="B12" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,39 +1775,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680425</v>
+        <v>680420</v>
       </c>
       <c r="R12" t="n">
-        <v>6601193</v>
+        <v>6601183</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,6 +1852,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1866,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121412758</v>
+        <v>121412572</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
+        <v>91325</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,46 +1887,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680420</v>
+        <v>680485</v>
       </c>
       <c r="R13" t="n">
-        <v>6601183</v>
+        <v>6601135</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,7 +1955,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121410851</v>
+        <v>121413970</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>5169</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,38 +1985,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680816</v>
+        <v>680380</v>
       </c>
       <c r="R14" t="n">
-        <v>6601025</v>
+        <v>6601066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,6 +2066,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2080,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121412680</v>
+        <v>121413912</v>
       </c>
       <c r="B15" t="n">
-        <v>95680</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,38 +2097,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680489</v>
+        <v>680381</v>
       </c>
       <c r="R15" t="n">
-        <v>6601147</v>
+        <v>6601114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,19 +2166,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2183,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414121</v>
+        <v>121411439</v>
       </c>
       <c r="B16" t="n">
-        <v>5169</v>
+        <v>8421</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,43 +2211,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680458</v>
+        <v>680555</v>
       </c>
       <c r="R16" t="n">
-        <v>6601079</v>
+        <v>6601112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2284,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121412711</v>
+        <v>121411191</v>
       </c>
       <c r="B17" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,42 +2318,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680420</v>
+        <v>680709</v>
       </c>
       <c r="R17" t="n">
-        <v>6601183</v>
+        <v>6601109</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,7 +2409,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121411092</v>
+        <v>121414014</v>
       </c>
       <c r="B18" t="n">
         <v>57367</v>
@@ -2448,21 +2443,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680739</v>
+        <v>680401</v>
       </c>
       <c r="R18" t="n">
-        <v>6601133</v>
+        <v>6601033</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121410676</v>
+        <v>121412669</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>95681</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,39 +2535,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680680</v>
+        <v>680434</v>
       </c>
       <c r="R19" t="n">
-        <v>6601025</v>
+        <v>6601196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121413923</v>
+        <v>121411092</v>
       </c>
       <c r="B20" t="n">
-        <v>57242</v>
+        <v>57367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2644,16 +2637,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2662,24 +2655,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680385</v>
+        <v>680739</v>
       </c>
       <c r="R20" t="n">
-        <v>6601107</v>
+        <v>6601133</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121410856</v>
+        <v>121412820</v>
       </c>
       <c r="B21" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,43 +2740,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680820</v>
+        <v>680357</v>
       </c>
       <c r="R21" t="n">
-        <v>6601031</v>
+        <v>6601265</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121412770</v>
+        <v>121414121</v>
       </c>
       <c r="B22" t="n">
-        <v>8421</v>
+        <v>5169</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2861,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2894,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680419</v>
+        <v>680458</v>
       </c>
       <c r="R22" t="n">
-        <v>6601182</v>
+        <v>6601079</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121412572</v>
+        <v>121411085</v>
       </c>
       <c r="B23" t="n">
-        <v>91324</v>
+        <v>57504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,41 +2962,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680485</v>
+        <v>680741</v>
       </c>
       <c r="R23" t="n">
-        <v>6601135</v>
+        <v>6601120</v>
       </c>
       <c r="S23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121414195</v>
+        <v>121412634</v>
       </c>
       <c r="B24" t="n">
-        <v>95680</v>
+        <v>5189</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3075,34 +3076,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680470</v>
+        <v>680449</v>
       </c>
       <c r="R24" t="n">
-        <v>6601110</v>
+        <v>6601206</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3161,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121414014</v>
+        <v>121412770</v>
       </c>
       <c r="B25" t="n">
-        <v>57367</v>
+        <v>8421</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,33 +3179,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3209,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680401</v>
+        <v>680419</v>
       </c>
       <c r="R25" t="n">
-        <v>6601033</v>
+        <v>6601182</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,6 +3260,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3271,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121412820</v>
+        <v>121414116</v>
       </c>
       <c r="B26" t="n">
-        <v>57367</v>
+        <v>90710</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3287,42 +3295,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680357</v>
+        <v>680468</v>
       </c>
       <c r="R26" t="n">
-        <v>6601265</v>
+        <v>6601091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121413892</v>
+        <v>121410851</v>
       </c>
       <c r="B27" t="n">
-        <v>57367</v>
+        <v>90710</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3397,42 +3397,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680392</v>
+        <v>680816</v>
       </c>
       <c r="R27" t="n">
-        <v>6601145</v>
+        <v>6601025</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,10 +3483,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121412634</v>
+        <v>121411550</v>
       </c>
       <c r="B28" t="n">
-        <v>5189</v>
+        <v>90710</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3503,43 +3495,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680449</v>
+        <v>680577</v>
       </c>
       <c r="R28" t="n">
-        <v>6601206</v>
+        <v>6601111</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3569,9 +3556,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,22 +3583,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121410858</v>
+        <v>121412711</v>
       </c>
       <c r="B29" t="n">
-        <v>5189</v>
+        <v>57504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3610,43 +3607,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680820</v>
+        <v>680420</v>
       </c>
       <c r="R29" t="n">
-        <v>6601031</v>
+        <v>6601183</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121412576</v>
+        <v>121412767</v>
       </c>
       <c r="B30" t="n">
         <v>57367</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680490</v>
+        <v>680411</v>
       </c>
       <c r="R30" t="n">
-        <v>6601144</v>
+        <v>6601181</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121411500</v>
+        <v>121412576</v>
       </c>
       <c r="B31" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3827,43 +3827,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680512</v>
+        <v>680490</v>
       </c>
       <c r="R31" t="n">
-        <v>6601083</v>
+        <v>6601144</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,10 +3925,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121414116</v>
+        <v>121411444</v>
       </c>
       <c r="B32" t="n">
-        <v>90709</v>
+        <v>57367</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,34 +3941,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680468</v>
+        <v>680555</v>
       </c>
       <c r="R32" t="n">
-        <v>6601091</v>
+        <v>6601110</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,10 +4032,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121412669</v>
+        <v>121414195</v>
       </c>
       <c r="B33" t="n">
-        <v>95680</v>
+        <v>95681</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4064,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680434</v>
+        <v>680470</v>
       </c>
       <c r="R33" t="n">
-        <v>6601196</v>
+        <v>6601110</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121412767</v>
+        <v>121410996</v>
       </c>
       <c r="B34" t="n">
-        <v>57367</v>
+        <v>100361</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,46 +4146,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680411</v>
+        <v>680804</v>
       </c>
       <c r="R34" t="n">
-        <v>6601181</v>
+        <v>6601124</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
         <v>121411629</v>
       </c>
       <c r="B35" t="n">
-        <v>95680</v>
+        <v>95681</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121413892</v>
+        <v>121412576</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680392</v>
+        <v>680490</v>
       </c>
       <c r="R2" t="n">
-        <v>6601145</v>
+        <v>6601144</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121412756</v>
+        <v>121412767</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680420</v>
+        <v>680411</v>
       </c>
       <c r="R3" t="n">
-        <v>6601183</v>
+        <v>6601181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121411749</v>
+        <v>121412758</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>8435</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,39 +911,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680501</v>
+        <v>680420</v>
       </c>
       <c r="R4" t="n">
-        <v>6601197</v>
+        <v>6601183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410676</v>
+        <v>121411085</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,46 +1019,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680680</v>
+        <v>680741</v>
       </c>
       <c r="R5" t="n">
-        <v>6601025</v>
+        <v>6601120</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121412678</v>
+        <v>121414014</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,43 +1129,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680425</v>
+        <v>680401</v>
       </c>
       <c r="R6" t="n">
-        <v>6601193</v>
+        <v>6601033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121412680</v>
+        <v>121411444</v>
       </c>
       <c r="B7" t="n">
-        <v>95681</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,38 +1239,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680489</v>
+        <v>680555</v>
       </c>
       <c r="R7" t="n">
-        <v>6601147</v>
+        <v>6601110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,19 +1305,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,22 +1322,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121410858</v>
+        <v>121412770</v>
       </c>
       <c r="B8" t="n">
-        <v>5189</v>
+        <v>8424</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,39 +1350,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680820</v>
+        <v>680419</v>
       </c>
       <c r="R8" t="n">
-        <v>6601031</v>
+        <v>6601182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,6 +1427,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121413923</v>
+        <v>121411191</v>
       </c>
       <c r="B9" t="n">
-        <v>57242</v>
+        <v>57370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,16 +1462,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1469,24 +1480,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680385</v>
+        <v>680709</v>
       </c>
       <c r="R9" t="n">
-        <v>6601107</v>
+        <v>6601109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121410856</v>
+        <v>121412680</v>
       </c>
       <c r="B10" t="n">
-        <v>5169</v>
+        <v>95684</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,39 +1569,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680820</v>
+        <v>680489</v>
       </c>
       <c r="R10" t="n">
-        <v>6601031</v>
+        <v>6601147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,9 +1626,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,22 +1653,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411500</v>
+        <v>121412572</v>
       </c>
       <c r="B11" t="n">
-        <v>5169</v>
+        <v>91328</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,42 +1681,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680512</v>
+        <v>680485</v>
       </c>
       <c r="R11" t="n">
-        <v>6601083</v>
+        <v>6601135</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121412758</v>
+        <v>121414116</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,47 +1779,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680420</v>
+        <v>680468</v>
       </c>
       <c r="R12" t="n">
-        <v>6601183</v>
+        <v>6601091</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1851,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1871,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121412572</v>
+        <v>121410996</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>100364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,13 +1909,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680485</v>
+        <v>680804</v>
       </c>
       <c r="R13" t="n">
-        <v>6601135</v>
+        <v>6601124</v>
       </c>
       <c r="S13" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121413970</v>
+        <v>121412678</v>
       </c>
       <c r="B14" t="n">
-        <v>5169</v>
+        <v>5172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2007,25 +2005,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680380</v>
+        <v>680425</v>
       </c>
       <c r="R14" t="n">
-        <v>6601066</v>
+        <v>6601193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2060,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2085,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121413912</v>
+        <v>121414195</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>95684</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,46 +2090,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680381</v>
+        <v>680470</v>
       </c>
       <c r="R15" t="n">
-        <v>6601114</v>
+        <v>6601110</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121411439</v>
+        <v>121410858</v>
       </c>
       <c r="B16" t="n">
-        <v>8421</v>
+        <v>5192</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2196,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680555</v>
+        <v>680820</v>
       </c>
       <c r="R16" t="n">
-        <v>6601112</v>
+        <v>6601031</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121411191</v>
+        <v>121410676</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,31 +2299,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2347,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680709</v>
+        <v>680680</v>
       </c>
       <c r="R17" t="n">
-        <v>6601109</v>
+        <v>6601025</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121414014</v>
+        <v>121410856</v>
       </c>
       <c r="B18" t="n">
-        <v>57367</v>
+        <v>5172</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,46 +2406,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680401</v>
+        <v>680820</v>
       </c>
       <c r="R18" t="n">
-        <v>6601033</v>
+        <v>6601031</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412669</v>
+        <v>121410851</v>
       </c>
       <c r="B19" t="n">
-        <v>95681</v>
+        <v>90713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2531,25 +2513,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680434</v>
+        <v>680816</v>
       </c>
       <c r="R19" t="n">
-        <v>6601196</v>
+        <v>6601025</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121411092</v>
+        <v>121412756</v>
       </c>
       <c r="B20" t="n">
-        <v>57367</v>
+        <v>57723</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,20 +2615,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2655,21 +2637,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680739</v>
+        <v>680420</v>
       </c>
       <c r="R20" t="n">
-        <v>6601133</v>
+        <v>6601183</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121412820</v>
+        <v>121411439</v>
       </c>
       <c r="B21" t="n">
-        <v>57367</v>
+        <v>8424</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,46 +2725,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680357</v>
+        <v>680555</v>
       </c>
       <c r="R21" t="n">
-        <v>6601265</v>
+        <v>6601112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121414121</v>
+        <v>121411550</v>
       </c>
       <c r="B22" t="n">
-        <v>5169</v>
+        <v>90713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,47 +2832,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680458</v>
+        <v>680577</v>
       </c>
       <c r="R22" t="n">
-        <v>6601079</v>
+        <v>6601111</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,40 +2893,49 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121411085</v>
+        <v>121413923</v>
       </c>
       <c r="B23" t="n">
-        <v>57504</v>
+        <v>57245</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2988,7 +2970,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2998,13 +2980,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680741</v>
+        <v>680385</v>
       </c>
       <c r="R23" t="n">
-        <v>6601120</v>
+        <v>6601107</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3060,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121412634</v>
+        <v>121411092</v>
       </c>
       <c r="B24" t="n">
-        <v>5189</v>
+        <v>57370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3072,20 +3054,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3096,7 +3078,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3105,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680449</v>
+        <v>680739</v>
       </c>
       <c r="R24" t="n">
-        <v>6601206</v>
+        <v>6601133</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3167,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121412770</v>
+        <v>121412820</v>
       </c>
       <c r="B25" t="n">
-        <v>8421</v>
+        <v>57370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3179,34 +3161,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3216,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680419</v>
+        <v>680357</v>
       </c>
       <c r="R25" t="n">
-        <v>6601182</v>
+        <v>6601265</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,7 +3241,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3279,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121414116</v>
+        <v>121412634</v>
       </c>
       <c r="B26" t="n">
-        <v>90710</v>
+        <v>5192</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3291,38 +3271,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680468</v>
+        <v>680449</v>
       </c>
       <c r="R26" t="n">
-        <v>6601091</v>
+        <v>6601206</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,10 +3366,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121410851</v>
+        <v>121411749</v>
       </c>
       <c r="B27" t="n">
-        <v>90710</v>
+        <v>8424</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3393,38 +3378,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680816</v>
+        <v>680501</v>
       </c>
       <c r="R27" t="n">
-        <v>6601025</v>
+        <v>6601197</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,10 +3473,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121411550</v>
+        <v>121412669</v>
       </c>
       <c r="B28" t="n">
-        <v>90710</v>
+        <v>95684</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3495,38 +3485,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680577</v>
+        <v>680434</v>
       </c>
       <c r="R28" t="n">
-        <v>6601111</v>
+        <v>6601196</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3556,19 +3546,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,22 +3563,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121412711</v>
+        <v>121413892</v>
       </c>
       <c r="B29" t="n">
-        <v>57504</v>
+        <v>57370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3611,21 +3591,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3633,7 +3613,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3643,10 +3623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680420</v>
+        <v>680392</v>
       </c>
       <c r="R29" t="n">
-        <v>6601183</v>
+        <v>6601145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121412767</v>
+        <v>121414121</v>
       </c>
       <c r="B30" t="n">
-        <v>57367</v>
+        <v>5172</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3717,33 +3697,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3753,10 +3734,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680411</v>
+        <v>680458</v>
       </c>
       <c r="R30" t="n">
-        <v>6601181</v>
+        <v>6601079</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,6 +3778,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3815,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121412576</v>
+        <v>121413912</v>
       </c>
       <c r="B31" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3863,10 +3845,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680490</v>
+        <v>680381</v>
       </c>
       <c r="R31" t="n">
-        <v>6601144</v>
+        <v>6601114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3925,10 +3907,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121411444</v>
+        <v>121411500</v>
       </c>
       <c r="B32" t="n">
-        <v>57367</v>
+        <v>5172</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3937,31 +3919,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3970,10 +3952,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680555</v>
+        <v>680512</v>
       </c>
       <c r="R32" t="n">
-        <v>6601110</v>
+        <v>6601083</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4032,10 +4014,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121414195</v>
+        <v>121413970</v>
       </c>
       <c r="B33" t="n">
-        <v>95681</v>
+        <v>5172</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4048,34 +4030,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680470</v>
+        <v>680380</v>
       </c>
       <c r="R33" t="n">
-        <v>6601110</v>
+        <v>6601066</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4116,6 +4107,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4134,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121410996</v>
+        <v>121412711</v>
       </c>
       <c r="B34" t="n">
-        <v>100361</v>
+        <v>57507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4146,38 +4138,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680804</v>
+        <v>680420</v>
       </c>
       <c r="R34" t="n">
-        <v>6601124</v>
+        <v>6601183</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
         <v>121411629</v>
       </c>
       <c r="B35" t="n">
-        <v>95681</v>
+        <v>95684</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121412576</v>
+        <v>121414195</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>95684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680490</v>
+        <v>680470</v>
       </c>
       <c r="R2" t="n">
-        <v>6601144</v>
+        <v>6601110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121412767</v>
+        <v>121411749</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>8424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,46 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680411</v>
+        <v>680501</v>
       </c>
       <c r="R3" t="n">
-        <v>6601181</v>
+        <v>6601197</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121412758</v>
+        <v>121413912</v>
       </c>
       <c r="B4" t="n">
-        <v>8435</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,34 +896,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680420</v>
+        <v>680381</v>
       </c>
       <c r="R4" t="n">
-        <v>6601183</v>
+        <v>6601114</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121411085</v>
+        <v>121413892</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,7 +1032,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1055,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680741</v>
+        <v>680392</v>
       </c>
       <c r="R5" t="n">
-        <v>6601120</v>
+        <v>6601145</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121414014</v>
+        <v>121410851</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,42 +1120,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680401</v>
+        <v>680816</v>
       </c>
       <c r="R6" t="n">
-        <v>6601033</v>
+        <v>6601025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121411444</v>
+        <v>121411439</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>8424</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,31 +1218,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1275,7 +1254,7 @@
         <v>680555</v>
       </c>
       <c r="R7" t="n">
-        <v>6601110</v>
+        <v>6601112</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121412770</v>
+        <v>121412711</v>
       </c>
       <c r="B8" t="n">
-        <v>8424</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,34 +1325,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1383,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680419</v>
+        <v>680420</v>
       </c>
       <c r="R8" t="n">
-        <v>6601182</v>
+        <v>6601183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1405,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1553,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121412680</v>
+        <v>121411085</v>
       </c>
       <c r="B10" t="n">
-        <v>95684</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,41 +1542,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680489</v>
+        <v>680741</v>
       </c>
       <c r="R10" t="n">
-        <v>6601147</v>
+        <v>6601120</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,19 +1611,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,22 +1628,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121412572</v>
+        <v>121412669</v>
       </c>
       <c r="B11" t="n">
-        <v>91328</v>
+        <v>95684</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,21 +1656,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,13 +1680,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680485</v>
+        <v>680434</v>
       </c>
       <c r="R11" t="n">
-        <v>6601135</v>
+        <v>6601196</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121414116</v>
+        <v>121413970</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>5172</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,38 +1754,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680468</v>
+        <v>680380</v>
       </c>
       <c r="R12" t="n">
-        <v>6601091</v>
+        <v>6601066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,6 +1835,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1869,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121410996</v>
+        <v>121414116</v>
       </c>
       <c r="B13" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,25 +1866,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680804</v>
+        <v>680468</v>
       </c>
       <c r="R13" t="n">
-        <v>6601124</v>
+        <v>6601091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121412678</v>
+        <v>121411550</v>
       </c>
       <c r="B14" t="n">
-        <v>5172</v>
+        <v>90713</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,43 +1968,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680425</v>
+        <v>680577</v>
       </c>
       <c r="R14" t="n">
-        <v>6601193</v>
+        <v>6601111</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,9 +2029,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,22 +2056,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121414195</v>
+        <v>121412820</v>
       </c>
       <c r="B15" t="n">
-        <v>95684</v>
+        <v>57370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,38 +2080,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680470</v>
+        <v>680357</v>
       </c>
       <c r="R15" t="n">
-        <v>6601110</v>
+        <v>6601265</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121410858</v>
+        <v>121412767</v>
       </c>
       <c r="B16" t="n">
-        <v>5192</v>
+        <v>57370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,20 +2190,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2214,21 +2212,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680820</v>
+        <v>680411</v>
       </c>
       <c r="R16" t="n">
-        <v>6601031</v>
+        <v>6601181</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121410676</v>
+        <v>121410996</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>100364</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,39 +2304,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680680</v>
+        <v>680804</v>
       </c>
       <c r="R17" t="n">
-        <v>6601025</v>
+        <v>6601124</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121410856</v>
+        <v>121414121</v>
       </c>
       <c r="B18" t="n">
         <v>5172</v>
@@ -2428,21 +2424,25 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680820</v>
+        <v>680458</v>
       </c>
       <c r="R18" t="n">
-        <v>6601031</v>
+        <v>6601079</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,6 +2483,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2501,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121410851</v>
+        <v>121412678</v>
       </c>
       <c r="B19" t="n">
-        <v>90713</v>
+        <v>5172</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,38 +2514,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680816</v>
+        <v>680425</v>
       </c>
       <c r="R19" t="n">
-        <v>6601025</v>
+        <v>6601193</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121412756</v>
+        <v>121412680</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>95684</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,42 +2625,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680420</v>
+        <v>680489</v>
       </c>
       <c r="R20" t="n">
-        <v>6601183</v>
+        <v>6601147</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,9 +2682,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,22 +2709,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121411439</v>
+        <v>121411444</v>
       </c>
       <c r="B21" t="n">
-        <v>8424</v>
+        <v>57370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,31 +2733,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2761,7 +2769,7 @@
         <v>680555</v>
       </c>
       <c r="R21" t="n">
-        <v>6601112</v>
+        <v>6601110</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121411550</v>
+        <v>121414014</v>
       </c>
       <c r="B22" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,34 +2844,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680577</v>
+        <v>680401</v>
       </c>
       <c r="R22" t="n">
-        <v>6601111</v>
+        <v>6601033</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,19 +2909,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,22 +2926,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121413923</v>
+        <v>121412634</v>
       </c>
       <c r="B23" t="n">
-        <v>57245</v>
+        <v>5192</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2944,20 +2950,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100001</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2966,24 +2972,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680385</v>
+        <v>680449</v>
       </c>
       <c r="R23" t="n">
-        <v>6601107</v>
+        <v>6601206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121411092</v>
+        <v>121412758</v>
       </c>
       <c r="B24" t="n">
-        <v>57370</v>
+        <v>8435</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3054,43 +3057,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680739</v>
+        <v>680420</v>
       </c>
       <c r="R24" t="n">
-        <v>6601133</v>
+        <v>6601183</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,6 +3138,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3149,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121412820</v>
+        <v>121411500</v>
       </c>
       <c r="B25" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,46 +3169,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680357</v>
+        <v>680512</v>
       </c>
       <c r="R25" t="n">
-        <v>6601265</v>
+        <v>6601083</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,10 +3264,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121412634</v>
+        <v>121412756</v>
       </c>
       <c r="B26" t="n">
-        <v>5192</v>
+        <v>57723</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,16 +3280,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3293,21 +3298,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680449</v>
+        <v>680420</v>
       </c>
       <c r="R26" t="n">
-        <v>6601206</v>
+        <v>6601183</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,10 +3374,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121411749</v>
+        <v>121412576</v>
       </c>
       <c r="B27" t="n">
-        <v>8424</v>
+        <v>57370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3378,43 +3386,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680501</v>
+        <v>680490</v>
       </c>
       <c r="R27" t="n">
-        <v>6601197</v>
+        <v>6601144</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,10 +3484,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121412669</v>
+        <v>121411092</v>
       </c>
       <c r="B28" t="n">
-        <v>95684</v>
+        <v>57370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3485,38 +3496,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680434</v>
+        <v>680739</v>
       </c>
       <c r="R28" t="n">
-        <v>6601196</v>
+        <v>6601133</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,10 +3591,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121413892</v>
+        <v>121410676</v>
       </c>
       <c r="B29" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3587,46 +3603,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680392</v>
+        <v>680680</v>
       </c>
       <c r="R29" t="n">
-        <v>6601145</v>
+        <v>6601025</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3698,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121414121</v>
+        <v>121410856</v>
       </c>
       <c r="B30" t="n">
         <v>5172</v>
@@ -3719,25 +3732,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680458</v>
+        <v>680820</v>
       </c>
       <c r="R30" t="n">
-        <v>6601079</v>
+        <v>6601031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3787,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3797,10 +3805,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121413912</v>
+        <v>121413923</v>
       </c>
       <c r="B31" t="n">
-        <v>57370</v>
+        <v>57245</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3813,16 +3821,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3835,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3845,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680381</v>
+        <v>680385</v>
       </c>
       <c r="R31" t="n">
-        <v>6601114</v>
+        <v>6601107</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121411500</v>
+        <v>121412770</v>
       </c>
       <c r="B32" t="n">
-        <v>5172</v>
+        <v>8424</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3923,39 +3931,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680512</v>
+        <v>680419</v>
       </c>
       <c r="R32" t="n">
-        <v>6601083</v>
+        <v>6601182</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,6 +4008,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4014,10 +4027,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121413970</v>
+        <v>121412572</v>
       </c>
       <c r="B33" t="n">
-        <v>5172</v>
+        <v>91328</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4030,46 +4043,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680380</v>
+        <v>680485</v>
       </c>
       <c r="R33" t="n">
-        <v>6601066</v>
+        <v>6601135</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4107,7 +4111,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4126,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121412711</v>
+        <v>121410858</v>
       </c>
       <c r="B34" t="n">
-        <v>57507</v>
+        <v>5192</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,46 +4141,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680420</v>
+        <v>680820</v>
       </c>
       <c r="R34" t="n">
-        <v>6601183</v>
+        <v>6601031</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121412669</v>
+        <v>121413970</v>
       </c>
       <c r="B11" t="n">
-        <v>95684</v>
+        <v>5172</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,34 +1656,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680434</v>
+        <v>680380</v>
       </c>
       <c r="R11" t="n">
-        <v>6601196</v>
+        <v>6601066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,6 +1733,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121413970</v>
+        <v>121414116</v>
       </c>
       <c r="B12" t="n">
-        <v>5172</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,47 +1764,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680380</v>
+        <v>680468</v>
       </c>
       <c r="R12" t="n">
-        <v>6601066</v>
+        <v>6601091</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1836,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414116</v>
+        <v>121411550</v>
       </c>
       <c r="B13" t="n">
         <v>90713</v>
@@ -1890,14 +1890,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680468</v>
+        <v>680577</v>
       </c>
       <c r="R13" t="n">
-        <v>6601091</v>
+        <v>6601111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,9 +1927,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,22 +1954,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121411550</v>
+        <v>121412669</v>
       </c>
       <c r="B14" t="n">
-        <v>90713</v>
+        <v>95684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,38 +1978,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680577</v>
+        <v>680434</v>
       </c>
       <c r="R14" t="n">
-        <v>6601111</v>
+        <v>6601196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,19 +2039,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,12 +2056,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121412767</v>
+        <v>121414121</v>
       </c>
       <c r="B16" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,33 +2190,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2226,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680411</v>
+        <v>680458</v>
       </c>
       <c r="R16" t="n">
-        <v>6601181</v>
+        <v>6601079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,6 +2271,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2288,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121410996</v>
+        <v>121412678</v>
       </c>
       <c r="B17" t="n">
-        <v>100364</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,34 +2306,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680804</v>
+        <v>680425</v>
       </c>
       <c r="R17" t="n">
-        <v>6601124</v>
+        <v>6601193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121414121</v>
+        <v>121412767</v>
       </c>
       <c r="B18" t="n">
-        <v>5172</v>
+        <v>57370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,34 +2409,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2439,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680458</v>
+        <v>680411</v>
       </c>
       <c r="R18" t="n">
-        <v>6601079</v>
+        <v>6601181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,7 +2489,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2502,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412678</v>
+        <v>121410996</v>
       </c>
       <c r="B19" t="n">
-        <v>5172</v>
+        <v>100364</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,39 +2523,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680425</v>
+        <v>680804</v>
       </c>
       <c r="R19" t="n">
-        <v>6601193</v>
+        <v>6601124</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121411444</v>
+        <v>121414014</v>
       </c>
       <c r="B21" t="n">
         <v>57370</v>
@@ -2755,21 +2755,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680555</v>
+        <v>680401</v>
       </c>
       <c r="R21" t="n">
-        <v>6601110</v>
+        <v>6601033</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2831,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121414014</v>
+        <v>121411444</v>
       </c>
       <c r="B22" t="n">
         <v>57370</v>
@@ -2862,24 +2865,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680401</v>
+        <v>680555</v>
       </c>
       <c r="R22" t="n">
-        <v>6601033</v>
+        <v>6601110</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413912</v>
+        <v>121410851</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680381</v>
+        <v>680816</v>
       </c>
       <c r="R4" t="n">
-        <v>6601114</v>
+        <v>6601025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121413892</v>
+        <v>121413912</v>
       </c>
       <c r="B5" t="n">
         <v>57370</v>
@@ -1042,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680392</v>
+        <v>680381</v>
       </c>
       <c r="R5" t="n">
-        <v>6601145</v>
+        <v>6601114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121410851</v>
+        <v>121413892</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,34 +1112,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680816</v>
+        <v>680392</v>
       </c>
       <c r="R6" t="n">
-        <v>6601025</v>
+        <v>6601145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121413970</v>
+        <v>121412669</v>
       </c>
       <c r="B11" t="n">
-        <v>5172</v>
+        <v>95684</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,43 +1656,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680380</v>
+        <v>680434</v>
       </c>
       <c r="R11" t="n">
-        <v>6601066</v>
+        <v>6601196</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1724,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121414116</v>
+        <v>121413970</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>5172</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,38 +1754,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680468</v>
+        <v>680380</v>
       </c>
       <c r="R12" t="n">
-        <v>6601091</v>
+        <v>6601066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,6 +1835,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121411550</v>
+        <v>121414116</v>
       </c>
       <c r="B13" t="n">
         <v>90713</v>
@@ -1890,14 +1890,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680577</v>
+        <v>680468</v>
       </c>
       <c r="R13" t="n">
-        <v>6601111</v>
+        <v>6601091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,19 +1927,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,22 +1944,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121412669</v>
+        <v>121411550</v>
       </c>
       <c r="B14" t="n">
-        <v>95684</v>
+        <v>90713</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,38 +1968,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680434</v>
+        <v>680577</v>
       </c>
       <c r="R14" t="n">
-        <v>6601196</v>
+        <v>6601111</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,9 +2029,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,12 +2056,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121414014</v>
+        <v>121411444</v>
       </c>
       <c r="B21" t="n">
         <v>57370</v>
@@ -2755,24 +2755,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680401</v>
+        <v>680555</v>
       </c>
       <c r="R21" t="n">
-        <v>6601033</v>
+        <v>6601110</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121411444</v>
+        <v>121414014</v>
       </c>
       <c r="B22" t="n">
         <v>57370</v>
@@ -2865,21 +2862,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680555</v>
+        <v>680401</v>
       </c>
       <c r="R22" t="n">
-        <v>6601110</v>
+        <v>6601033</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121414195</v>
+        <v>121411444</v>
       </c>
       <c r="B2" t="n">
-        <v>95684</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680470</v>
+        <v>680555</v>
       </c>
       <c r="R2" t="n">
         <v>6601110</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121411749</v>
+        <v>121410851</v>
       </c>
       <c r="B3" t="n">
-        <v>8424</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680501</v>
+        <v>680816</v>
       </c>
       <c r="R3" t="n">
-        <v>6601197</v>
+        <v>6601025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410851</v>
+        <v>121412572</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>91334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680816</v>
+        <v>680485</v>
       </c>
       <c r="R4" t="n">
-        <v>6601025</v>
+        <v>6601135</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121413912</v>
+        <v>121412680</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>95690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,46 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680381</v>
+        <v>680489</v>
       </c>
       <c r="R5" t="n">
-        <v>6601114</v>
+        <v>6601147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,9 +1059,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121413892</v>
+        <v>121411550</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>90719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,42 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680392</v>
+        <v>680577</v>
       </c>
       <c r="R6" t="n">
-        <v>6601145</v>
+        <v>6601111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,9 +1171,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,12 +1198,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121412711</v>
+        <v>121414116</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>90719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,42 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680420</v>
+        <v>680468</v>
       </c>
       <c r="R8" t="n">
-        <v>6601183</v>
+        <v>6601091</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121411191</v>
+        <v>121412770</v>
       </c>
       <c r="B9" t="n">
-        <v>57370</v>
+        <v>8424</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,43 +1431,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680709</v>
+        <v>680419</v>
       </c>
       <c r="R9" t="n">
-        <v>6601109</v>
+        <v>6601182</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,6 +1512,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1530,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411085</v>
+        <v>121412758</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>8435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,33 +1543,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1578,13 +1580,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680741</v>
+        <v>680420</v>
       </c>
       <c r="R10" t="n">
-        <v>6601120</v>
+        <v>6601183</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,6 +1624,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1640,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121412669</v>
+        <v>121411191</v>
       </c>
       <c r="B11" t="n">
-        <v>95684</v>
+        <v>57371</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,38 +1655,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680434</v>
+        <v>680709</v>
       </c>
       <c r="R11" t="n">
-        <v>6601196</v>
+        <v>6601109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121413970</v>
+        <v>121413912</v>
       </c>
       <c r="B12" t="n">
-        <v>5172</v>
+        <v>57371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,34 +1762,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1791,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680380</v>
+        <v>680381</v>
       </c>
       <c r="R12" t="n">
-        <v>6601066</v>
+        <v>6601114</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1854,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121414116</v>
+        <v>121412820</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>57371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,34 +1876,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680468</v>
+        <v>680357</v>
       </c>
       <c r="R13" t="n">
-        <v>6601091</v>
+        <v>6601265</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121411550</v>
+        <v>121411749</v>
       </c>
       <c r="B14" t="n">
-        <v>90713</v>
+        <v>8424</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,38 +1982,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680577</v>
+        <v>680501</v>
       </c>
       <c r="R14" t="n">
-        <v>6601111</v>
+        <v>6601197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,19 +2048,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,22 +2065,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121412820</v>
+        <v>121414014</v>
       </c>
       <c r="B15" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2116,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680357</v>
+        <v>680401</v>
       </c>
       <c r="R15" t="n">
-        <v>6601265</v>
+        <v>6601033</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414121</v>
+        <v>121410858</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,43 +2203,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680458</v>
+        <v>680820</v>
       </c>
       <c r="R16" t="n">
-        <v>6601079</v>
+        <v>6601031</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2276,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2290,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121412678</v>
+        <v>121410996</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>100370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,39 +2310,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680425</v>
+        <v>680804</v>
       </c>
       <c r="R17" t="n">
-        <v>6601193</v>
+        <v>6601124</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121412767</v>
+        <v>121412669</v>
       </c>
       <c r="B18" t="n">
-        <v>57370</v>
+        <v>95690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,46 +2408,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680411</v>
+        <v>680434</v>
       </c>
       <c r="R18" t="n">
-        <v>6601181</v>
+        <v>6601196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121410996</v>
+        <v>121411092</v>
       </c>
       <c r="B19" t="n">
-        <v>100364</v>
+        <v>57371</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,38 +2510,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680804</v>
+        <v>680739</v>
       </c>
       <c r="R19" t="n">
-        <v>6601124</v>
+        <v>6601133</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121412680</v>
+        <v>121412711</v>
       </c>
       <c r="B20" t="n">
-        <v>95684</v>
+        <v>57508</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,38 +2617,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680489</v>
+        <v>680420</v>
       </c>
       <c r="R20" t="n">
-        <v>6601147</v>
+        <v>6601183</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,19 +2686,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,22 +2703,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121411444</v>
+        <v>121411085</v>
       </c>
       <c r="B21" t="n">
-        <v>57370</v>
+        <v>57508</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,42 +2731,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680555</v>
+        <v>680741</v>
       </c>
       <c r="R21" t="n">
-        <v>6601110</v>
+        <v>6601120</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2828,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121414014</v>
+        <v>121414121</v>
       </c>
       <c r="B22" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,33 +2837,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2876,10 +2874,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680401</v>
+        <v>680458</v>
       </c>
       <c r="R22" t="n">
-        <v>6601033</v>
+        <v>6601079</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,6 +2918,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2938,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121412634</v>
+        <v>121411500</v>
       </c>
       <c r="B23" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680449</v>
+        <v>680512</v>
       </c>
       <c r="R23" t="n">
-        <v>6601206</v>
+        <v>6601083</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121412758</v>
+        <v>121412634</v>
       </c>
       <c r="B24" t="n">
-        <v>8435</v>
+        <v>5192</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3061,43 +3060,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680420</v>
+        <v>680449</v>
       </c>
       <c r="R24" t="n">
-        <v>6601183</v>
+        <v>6601206</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,7 +3133,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3157,7 +3151,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121411500</v>
+        <v>121410856</v>
       </c>
       <c r="B25" t="n">
         <v>5172</v>
@@ -3202,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680512</v>
+        <v>680820</v>
       </c>
       <c r="R25" t="n">
-        <v>6601083</v>
+        <v>6601031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3264,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121412756</v>
+        <v>121413923</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57246</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3276,20 +3270,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3302,7 +3296,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3312,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680420</v>
+        <v>680385</v>
       </c>
       <c r="R26" t="n">
-        <v>6601183</v>
+        <v>6601107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3374,10 +3368,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121412576</v>
+        <v>121412756</v>
       </c>
       <c r="B27" t="n">
-        <v>57370</v>
+        <v>57724</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3386,20 +3380,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3412,7 +3406,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3422,10 +3416,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680490</v>
+        <v>680420</v>
       </c>
       <c r="R27" t="n">
-        <v>6601144</v>
+        <v>6601183</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,10 +3478,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121411092</v>
+        <v>121412678</v>
       </c>
       <c r="B28" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3496,31 +3490,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3529,10 +3523,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680739</v>
+        <v>680425</v>
       </c>
       <c r="R28" t="n">
-        <v>6601133</v>
+        <v>6601193</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,10 +3585,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121410676</v>
+        <v>121412576</v>
       </c>
       <c r="B29" t="n">
-        <v>5172</v>
+        <v>57371</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3603,43 +3597,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680680</v>
+        <v>680490</v>
       </c>
       <c r="R29" t="n">
-        <v>6601025</v>
+        <v>6601144</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121410856</v>
+        <v>121413892</v>
       </c>
       <c r="B30" t="n">
-        <v>5172</v>
+        <v>57371</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,43 +3707,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680820</v>
+        <v>680392</v>
       </c>
       <c r="R30" t="n">
-        <v>6601031</v>
+        <v>6601145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,10 +3805,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121413923</v>
+        <v>121412767</v>
       </c>
       <c r="B31" t="n">
-        <v>57245</v>
+        <v>57371</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3821,16 +3821,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680385</v>
+        <v>680411</v>
       </c>
       <c r="R31" t="n">
-        <v>6601107</v>
+        <v>6601181</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121412770</v>
+        <v>121414195</v>
       </c>
       <c r="B32" t="n">
-        <v>8424</v>
+        <v>95690</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3931,43 +3931,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>2590</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680419</v>
+        <v>680470</v>
       </c>
       <c r="R32" t="n">
-        <v>6601182</v>
+        <v>6601110</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4008,7 +3999,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4027,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121412572</v>
+        <v>121413970</v>
       </c>
       <c r="B33" t="n">
-        <v>91328</v>
+        <v>5172</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4043,37 +4033,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680485</v>
+        <v>680380</v>
       </c>
       <c r="R33" t="n">
-        <v>6601135</v>
+        <v>6601066</v>
       </c>
       <c r="S33" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4111,6 +4110,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121410858</v>
+        <v>121410676</v>
       </c>
       <c r="B34" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4145,21 +4145,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680820</v>
+        <v>680680</v>
       </c>
       <c r="R34" t="n">
-        <v>6601031</v>
+        <v>6601025</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
         <v>121411629</v>
       </c>
       <c r="B35" t="n">
-        <v>95684</v>
+        <v>95690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -2715,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121411085</v>
+        <v>121412634</v>
       </c>
       <c r="B21" t="n">
-        <v>57508</v>
+        <v>5192</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,49 +2727,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680741</v>
+        <v>680449</v>
       </c>
       <c r="R21" t="n">
-        <v>6601120</v>
+        <v>6601206</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2825,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121414121</v>
+        <v>121411085</v>
       </c>
       <c r="B22" t="n">
-        <v>5172</v>
+        <v>57508</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,34 +2834,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2874,13 +2870,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680458</v>
+        <v>680741</v>
       </c>
       <c r="R22" t="n">
-        <v>6601079</v>
+        <v>6601120</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2918,7 +2914,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2937,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121411500</v>
+        <v>121414121</v>
       </c>
       <c r="B23" t="n">
         <v>5172</v>
@@ -2971,21 +2966,25 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680512</v>
+        <v>680458</v>
       </c>
       <c r="R23" t="n">
-        <v>6601083</v>
+        <v>6601079</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,6 +3025,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121412634</v>
+        <v>121411500</v>
       </c>
       <c r="B24" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680449</v>
+        <v>680512</v>
       </c>
       <c r="R24" t="n">
-        <v>6601206</v>
+        <v>6601083</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121410856</v>
+        <v>121413923</v>
       </c>
       <c r="B25" t="n">
-        <v>5172</v>
+        <v>57246</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3163,43 +3163,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680820</v>
+        <v>680385</v>
       </c>
       <c r="R25" t="n">
-        <v>6601031</v>
+        <v>6601107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,10 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121413923</v>
+        <v>121410856</v>
       </c>
       <c r="B26" t="n">
-        <v>57246</v>
+        <v>5172</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3270,46 +3273,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680385</v>
+        <v>680820</v>
       </c>
       <c r="R26" t="n">
-        <v>6601107</v>
+        <v>6601031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121411444</v>
+        <v>121411500</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680555</v>
+        <v>680512</v>
       </c>
       <c r="R2" t="n">
-        <v>6601110</v>
+        <v>6601083</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410851</v>
+        <v>121411085</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +798,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680816</v>
+        <v>680741</v>
       </c>
       <c r="R3" t="n">
-        <v>6601025</v>
+        <v>6601120</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +895,7 @@
         <v>121412572</v>
       </c>
       <c r="B4" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121412680</v>
+        <v>121412711</v>
       </c>
       <c r="B5" t="n">
-        <v>95690</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +1006,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680489</v>
+        <v>680420</v>
       </c>
       <c r="R5" t="n">
-        <v>6601147</v>
+        <v>6601183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,19 +1075,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1092,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121411550</v>
+        <v>121412669</v>
       </c>
       <c r="B6" t="n">
-        <v>90719</v>
+        <v>95691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1116,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680577</v>
+        <v>680434</v>
       </c>
       <c r="R6" t="n">
-        <v>6601111</v>
+        <v>6601196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,19 +1177,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,22 +1194,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121411439</v>
+        <v>121411092</v>
       </c>
       <c r="B7" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,31 +1218,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680555</v>
+        <v>680739</v>
       </c>
       <c r="R7" t="n">
-        <v>6601112</v>
+        <v>6601133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121414116</v>
+        <v>121413970</v>
       </c>
       <c r="B8" t="n">
-        <v>90719</v>
+        <v>5172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,38 +1325,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680468</v>
+        <v>680380</v>
       </c>
       <c r="R8" t="n">
-        <v>6601091</v>
+        <v>6601066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,6 +1406,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1419,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121412770</v>
+        <v>121410676</v>
       </c>
       <c r="B9" t="n">
-        <v>8424</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,43 +1441,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680419</v>
+        <v>680680</v>
       </c>
       <c r="R9" t="n">
-        <v>6601182</v>
+        <v>6601025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1514,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121412758</v>
+        <v>121412678</v>
       </c>
       <c r="B10" t="n">
-        <v>8435</v>
+        <v>5172</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,43 +1548,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680420</v>
+        <v>680425</v>
       </c>
       <c r="R10" t="n">
-        <v>6601183</v>
+        <v>6601193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,7 +1621,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1643,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411191</v>
+        <v>121411439</v>
       </c>
       <c r="B11" t="n">
-        <v>57371</v>
+        <v>8424</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,31 +1651,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1688,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680709</v>
+        <v>680555</v>
       </c>
       <c r="R11" t="n">
-        <v>6601109</v>
+        <v>6601112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121413912</v>
+        <v>121410996</v>
       </c>
       <c r="B12" t="n">
-        <v>57371</v>
+        <v>100371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,46 +1758,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680381</v>
+        <v>680804</v>
       </c>
       <c r="R12" t="n">
-        <v>6601114</v>
+        <v>6601124</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121412820</v>
+        <v>121411444</v>
       </c>
       <c r="B13" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,24 +1882,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680357</v>
+        <v>680555</v>
       </c>
       <c r="R13" t="n">
-        <v>6601265</v>
+        <v>6601110</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121411749</v>
+        <v>121411191</v>
       </c>
       <c r="B14" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,31 +1967,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2015,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680501</v>
+        <v>680709</v>
       </c>
       <c r="R14" t="n">
-        <v>6601197</v>
+        <v>6601109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121414014</v>
+        <v>121412767</v>
       </c>
       <c r="B15" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680401</v>
+        <v>680411</v>
       </c>
       <c r="R15" t="n">
-        <v>6601033</v>
+        <v>6601181</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2172,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121410858</v>
+        <v>121410856</v>
       </c>
       <c r="B16" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,21 +2188,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121410996</v>
+        <v>121411749</v>
       </c>
       <c r="B17" t="n">
-        <v>100370</v>
+        <v>8424</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,34 +2295,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680804</v>
+        <v>680501</v>
       </c>
       <c r="R17" t="n">
-        <v>6601124</v>
+        <v>6601197</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121412669</v>
+        <v>121412758</v>
       </c>
       <c r="B18" t="n">
-        <v>95690</v>
+        <v>8435</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,34 +2402,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680434</v>
+        <v>680420</v>
       </c>
       <c r="R18" t="n">
-        <v>6601196</v>
+        <v>6601183</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,6 +2479,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121411092</v>
+        <v>121410851</v>
       </c>
       <c r="B19" t="n">
-        <v>57371</v>
+        <v>90720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,39 +2514,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680739</v>
+        <v>680816</v>
       </c>
       <c r="R19" t="n">
-        <v>6601133</v>
+        <v>6601025</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121412711</v>
+        <v>121414014</v>
       </c>
       <c r="B20" t="n">
-        <v>57508</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,21 +2616,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,7 +2638,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2653,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680420</v>
+        <v>680401</v>
       </c>
       <c r="R20" t="n">
-        <v>6601183</v>
+        <v>6601033</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,10 +2710,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121412634</v>
+        <v>121413912</v>
       </c>
       <c r="B21" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,20 +2722,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2749,21 +2744,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680449</v>
+        <v>680381</v>
       </c>
       <c r="R21" t="n">
-        <v>6601206</v>
+        <v>6601114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121411085</v>
+        <v>121412820</v>
       </c>
       <c r="B22" t="n">
-        <v>57508</v>
+        <v>57372</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2838,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,7 +2858,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2870,13 +2868,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680741</v>
+        <v>680357</v>
       </c>
       <c r="R22" t="n">
-        <v>6601120</v>
+        <v>6601265</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2932,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121414121</v>
+        <v>121412680</v>
       </c>
       <c r="B23" t="n">
-        <v>5172</v>
+        <v>95691</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,43 +2946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680458</v>
+        <v>680489</v>
       </c>
       <c r="R23" t="n">
-        <v>6601079</v>
+        <v>6601147</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,40 +3003,49 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121411500</v>
+        <v>121411550</v>
       </c>
       <c r="B24" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3056,43 +3054,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680512</v>
+        <v>680577</v>
       </c>
       <c r="R24" t="n">
-        <v>6601083</v>
+        <v>6601111</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,9 +3115,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,12 +3142,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3154,7 +3157,7 @@
         <v>121413923</v>
       </c>
       <c r="B25" t="n">
-        <v>57246</v>
+        <v>57247</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3261,10 +3264,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121410856</v>
+        <v>121414116</v>
       </c>
       <c r="B26" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3273,43 +3276,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680820</v>
+        <v>680468</v>
       </c>
       <c r="R26" t="n">
-        <v>6601031</v>
+        <v>6601091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,10 +3366,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121412756</v>
+        <v>121413892</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3380,20 +3378,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3406,7 +3404,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3416,10 +3414,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680420</v>
+        <v>680392</v>
       </c>
       <c r="R27" t="n">
-        <v>6601183</v>
+        <v>6601145</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3478,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121412678</v>
+        <v>121414195</v>
       </c>
       <c r="B28" t="n">
-        <v>5172</v>
+        <v>95691</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3494,39 +3492,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680425</v>
+        <v>680470</v>
       </c>
       <c r="R28" t="n">
-        <v>6601193</v>
+        <v>6601110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,7 +3581,7 @@
         <v>121412576</v>
       </c>
       <c r="B29" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3695,10 +3688,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121413892</v>
+        <v>121414121</v>
       </c>
       <c r="B30" t="n">
-        <v>57371</v>
+        <v>5172</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,33 +3700,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3743,10 +3737,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680392</v>
+        <v>680458</v>
       </c>
       <c r="R30" t="n">
-        <v>6601145</v>
+        <v>6601079</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3787,6 +3781,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3805,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121412767</v>
+        <v>121412634</v>
       </c>
       <c r="B31" t="n">
-        <v>57371</v>
+        <v>5192</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3817,20 +3812,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3839,24 +3834,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680411</v>
+        <v>680449</v>
       </c>
       <c r="R31" t="n">
-        <v>6601181</v>
+        <v>6601206</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,10 +3907,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121414195</v>
+        <v>121412770</v>
       </c>
       <c r="B32" t="n">
-        <v>95690</v>
+        <v>8424</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3931,34 +3923,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2590</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680470</v>
+        <v>680419</v>
       </c>
       <c r="R32" t="n">
-        <v>6601110</v>
+        <v>6601182</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,6 +4000,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4017,10 +4019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121413970</v>
+        <v>121412756</v>
       </c>
       <c r="B33" t="n">
-        <v>5172</v>
+        <v>57725</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4033,30 +4035,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4066,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680380</v>
+        <v>680420</v>
       </c>
       <c r="R33" t="n">
-        <v>6601066</v>
+        <v>6601183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,7 +4111,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121410676</v>
+        <v>121410858</v>
       </c>
       <c r="B34" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4145,21 +4145,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680680</v>
+        <v>680820</v>
       </c>
       <c r="R34" t="n">
-        <v>6601025</v>
+        <v>6601031</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
         <v>121411629</v>
       </c>
       <c r="B35" t="n">
-        <v>95690</v>
+        <v>95691</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121411500</v>
+        <v>121412680</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>95691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680512</v>
+        <v>680489</v>
       </c>
       <c r="R2" t="n">
-        <v>6601083</v>
+        <v>6601147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,9 +748,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121411085</v>
+        <v>121410676</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,49 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680741</v>
+        <v>680680</v>
       </c>
       <c r="R3" t="n">
-        <v>6601120</v>
+        <v>6601025</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121412572</v>
+        <v>121412576</v>
       </c>
       <c r="B4" t="n">
-        <v>91335</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,41 +906,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680485</v>
+        <v>680490</v>
       </c>
       <c r="R4" t="n">
-        <v>6601135</v>
+        <v>6601144</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121412711</v>
+        <v>121412678</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,46 +1016,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680420</v>
+        <v>680425</v>
       </c>
       <c r="R5" t="n">
-        <v>6601183</v>
+        <v>6601193</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121412669</v>
+        <v>121411092</v>
       </c>
       <c r="B6" t="n">
-        <v>95691</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,38 +1123,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680434</v>
+        <v>680739</v>
       </c>
       <c r="R6" t="n">
-        <v>6601196</v>
+        <v>6601133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121411092</v>
+        <v>121413970</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,43 +1230,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680739</v>
+        <v>680380</v>
       </c>
       <c r="R7" t="n">
-        <v>6601133</v>
+        <v>6601066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1311,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121413970</v>
+        <v>121412820</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,34 +1342,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1362,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680380</v>
+        <v>680357</v>
       </c>
       <c r="R8" t="n">
-        <v>6601066</v>
+        <v>6601265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1422,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,7 +1440,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121410676</v>
+        <v>121414121</v>
       </c>
       <c r="B9" t="n">
         <v>5172</v>
@@ -1459,21 +1474,25 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680680</v>
+        <v>680458</v>
       </c>
       <c r="R9" t="n">
-        <v>6601025</v>
+        <v>6601079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1533,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1532,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121412678</v>
+        <v>121412758</v>
       </c>
       <c r="B10" t="n">
-        <v>5172</v>
+        <v>8435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,39 +1568,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680425</v>
+        <v>680420</v>
       </c>
       <c r="R10" t="n">
-        <v>6601193</v>
+        <v>6601183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,6 +1645,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411439</v>
+        <v>121411191</v>
       </c>
       <c r="B11" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,31 +1676,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1684,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680555</v>
+        <v>680709</v>
       </c>
       <c r="R11" t="n">
-        <v>6601112</v>
+        <v>6601109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121410996</v>
+        <v>121412634</v>
       </c>
       <c r="B12" t="n">
-        <v>100371</v>
+        <v>5192</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,34 +1787,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680804</v>
+        <v>680449</v>
       </c>
       <c r="R12" t="n">
-        <v>6601124</v>
+        <v>6601206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121411444</v>
+        <v>121410996</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>100371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,43 +1890,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680555</v>
+        <v>680804</v>
       </c>
       <c r="R13" t="n">
-        <v>6601110</v>
+        <v>6601124</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121411191</v>
+        <v>121412669</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>95691</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,43 +1992,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680709</v>
+        <v>680434</v>
       </c>
       <c r="R14" t="n">
-        <v>6601109</v>
+        <v>6601196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121412767</v>
+        <v>121412711</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2098,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,7 +2120,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2110,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680411</v>
+        <v>680420</v>
       </c>
       <c r="R15" t="n">
-        <v>6601181</v>
+        <v>6601183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121410856</v>
+        <v>121414116</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,43 +2204,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680820</v>
+        <v>680468</v>
       </c>
       <c r="R16" t="n">
-        <v>6601031</v>
+        <v>6601091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2386,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121412758</v>
+        <v>121413923</v>
       </c>
       <c r="B18" t="n">
-        <v>8435</v>
+        <v>57247</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,34 +2413,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2435,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680420</v>
+        <v>680385</v>
       </c>
       <c r="R18" t="n">
-        <v>6601183</v>
+        <v>6601107</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2493,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2498,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121410851</v>
+        <v>121412572</v>
       </c>
       <c r="B19" t="n">
-        <v>90720</v>
+        <v>91335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,25 +2523,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,13 +2551,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680816</v>
+        <v>680485</v>
       </c>
       <c r="R19" t="n">
-        <v>6601025</v>
+        <v>6601135</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2600,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121414014</v>
+        <v>121411439</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>8424</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,46 +2625,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680401</v>
+        <v>680555</v>
       </c>
       <c r="R20" t="n">
-        <v>6601033</v>
+        <v>6601112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2710,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121413912</v>
+        <v>121410858</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>5192</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,20 +2732,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2744,24 +2754,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680381</v>
+        <v>680820</v>
       </c>
       <c r="R21" t="n">
-        <v>6601114</v>
+        <v>6601031</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,7 +2827,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121412820</v>
+        <v>121413892</v>
       </c>
       <c r="B22" t="n">
         <v>57372</v>
@@ -2868,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680357</v>
+        <v>680392</v>
       </c>
       <c r="R22" t="n">
-        <v>6601265</v>
+        <v>6601145</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121412680</v>
+        <v>121410856</v>
       </c>
       <c r="B23" t="n">
-        <v>95691</v>
+        <v>5172</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2946,34 +2953,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680489</v>
+        <v>680820</v>
       </c>
       <c r="R23" t="n">
-        <v>6601147</v>
+        <v>6601031</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,19 +3015,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3030,22 +3032,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121411550</v>
+        <v>121414014</v>
       </c>
       <c r="B24" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,34 +3060,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680577</v>
+        <v>680401</v>
       </c>
       <c r="R24" t="n">
-        <v>6601111</v>
+        <v>6601033</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,19 +3125,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3142,22 +3142,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121413923</v>
+        <v>121413912</v>
       </c>
       <c r="B25" t="n">
-        <v>57247</v>
+        <v>57372</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3192,7 +3192,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680385</v>
+        <v>680381</v>
       </c>
       <c r="R25" t="n">
-        <v>6601107</v>
+        <v>6601114</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121414116</v>
+        <v>121414195</v>
       </c>
       <c r="B26" t="n">
-        <v>90720</v>
+        <v>95691</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3276,25 +3276,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680468</v>
+        <v>680470</v>
       </c>
       <c r="R26" t="n">
-        <v>6601091</v>
+        <v>6601110</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,10 +3366,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121413892</v>
+        <v>121411085</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3382,21 +3382,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3414,13 +3414,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680392</v>
+        <v>680741</v>
       </c>
       <c r="R27" t="n">
-        <v>6601145</v>
+        <v>6601120</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121414195</v>
+        <v>121411444</v>
       </c>
       <c r="B28" t="n">
-        <v>95691</v>
+        <v>57372</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3488,35 +3488,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680470</v>
+        <v>680555</v>
       </c>
       <c r="R28" t="n">
         <v>6601110</v>
@@ -3578,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121412576</v>
+        <v>121411500</v>
       </c>
       <c r="B29" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3590,46 +3595,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680490</v>
+        <v>680512</v>
       </c>
       <c r="R29" t="n">
-        <v>6601144</v>
+        <v>6601083</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,10 +3690,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121414121</v>
+        <v>121410851</v>
       </c>
       <c r="B30" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3700,47 +3702,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680458</v>
+        <v>680816</v>
       </c>
       <c r="R30" t="n">
-        <v>6601079</v>
+        <v>6601025</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3774,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3800,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121412634</v>
+        <v>121411550</v>
       </c>
       <c r="B31" t="n">
-        <v>5192</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,43 +3804,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680449</v>
+        <v>680577</v>
       </c>
       <c r="R31" t="n">
-        <v>6601206</v>
+        <v>6601111</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,9 +3865,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,22 +3892,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121412770</v>
+        <v>121412767</v>
       </c>
       <c r="B32" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3919,34 +3916,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3956,10 +3952,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680419</v>
+        <v>680411</v>
       </c>
       <c r="R32" t="n">
-        <v>6601182</v>
+        <v>6601181</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,7 +3996,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4124,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121410858</v>
+        <v>121412770</v>
       </c>
       <c r="B34" t="n">
-        <v>5192</v>
+        <v>8424</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4145,39 +4140,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680820</v>
+        <v>680419</v>
       </c>
       <c r="R34" t="n">
-        <v>6601031</v>
+        <v>6601182</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4218,6 +4217,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121412680</v>
+        <v>121412669</v>
       </c>
       <c r="B2" t="n">
         <v>95691</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680489</v>
+        <v>680434</v>
       </c>
       <c r="R2" t="n">
-        <v>6601147</v>
+        <v>6601196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410676</v>
+        <v>121412756</v>
       </c>
       <c r="B3" t="n">
-        <v>5172</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680680</v>
+        <v>680420</v>
       </c>
       <c r="R3" t="n">
-        <v>6601025</v>
+        <v>6601183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121412576</v>
+        <v>121410996</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>100371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,46 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680490</v>
+        <v>680804</v>
       </c>
       <c r="R4" t="n">
-        <v>6601144</v>
+        <v>6601124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121412678</v>
+        <v>121413912</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,43 +1001,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680425</v>
+        <v>680381</v>
       </c>
       <c r="R5" t="n">
-        <v>6601193</v>
+        <v>6601114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121411092</v>
+        <v>121412634</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>5192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,20 +1111,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1147,7 +1135,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1156,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680739</v>
+        <v>680449</v>
       </c>
       <c r="R6" t="n">
-        <v>6601133</v>
+        <v>6601206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121413970</v>
+        <v>121411439</v>
       </c>
       <c r="B7" t="n">
-        <v>5172</v>
+        <v>8424</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,43 +1222,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680380</v>
+        <v>680555</v>
       </c>
       <c r="R7" t="n">
-        <v>6601066</v>
+        <v>6601112</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1295,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1330,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121412820</v>
+        <v>121412678</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,46 +1325,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680357</v>
+        <v>680425</v>
       </c>
       <c r="R8" t="n">
-        <v>6601265</v>
+        <v>6601193</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414121</v>
+        <v>121412680</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
+        <v>95691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,43 +1436,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680458</v>
+        <v>680489</v>
       </c>
       <c r="R9" t="n">
-        <v>6601079</v>
+        <v>6601147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,40 +1493,49 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121412758</v>
+        <v>121413923</v>
       </c>
       <c r="B10" t="n">
-        <v>8435</v>
+        <v>57247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,34 +1544,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1601,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680420</v>
+        <v>680385</v>
       </c>
       <c r="R10" t="n">
-        <v>6601183</v>
+        <v>6601107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,7 +1624,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1664,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411191</v>
+        <v>121412770</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>8424</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,43 +1654,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680709</v>
+        <v>680419</v>
       </c>
       <c r="R11" t="n">
-        <v>6601109</v>
+        <v>6601182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,6 +1735,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1771,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121412634</v>
+        <v>121410856</v>
       </c>
       <c r="B12" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680449</v>
+        <v>680820</v>
       </c>
       <c r="R12" t="n">
-        <v>6601206</v>
+        <v>6601031</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121410996</v>
+        <v>121411749</v>
       </c>
       <c r="B13" t="n">
-        <v>100371</v>
+        <v>8424</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,34 +1877,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680804</v>
+        <v>680501</v>
       </c>
       <c r="R13" t="n">
-        <v>6601124</v>
+        <v>6601197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121412669</v>
+        <v>121411085</v>
       </c>
       <c r="B14" t="n">
-        <v>95691</v>
+        <v>57509</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,41 +1980,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680434</v>
+        <v>680741</v>
       </c>
       <c r="R14" t="n">
-        <v>6601196</v>
+        <v>6601120</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121412711</v>
+        <v>121410851</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,42 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680420</v>
+        <v>680816</v>
       </c>
       <c r="R15" t="n">
-        <v>6601183</v>
+        <v>6601025</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414116</v>
+        <v>121414014</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,34 +2196,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680468</v>
+        <v>680401</v>
       </c>
       <c r="R16" t="n">
-        <v>6601091</v>
+        <v>6601033</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121411749</v>
+        <v>121411191</v>
       </c>
       <c r="B17" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,31 +2302,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2339,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680501</v>
+        <v>680709</v>
       </c>
       <c r="R17" t="n">
-        <v>6601197</v>
+        <v>6601109</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121413923</v>
+        <v>121411092</v>
       </c>
       <c r="B18" t="n">
-        <v>57247</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,16 +2413,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2435,24 +2431,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680385</v>
+        <v>680739</v>
       </c>
       <c r="R18" t="n">
-        <v>6601107</v>
+        <v>6601133</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412572</v>
+        <v>121413970</v>
       </c>
       <c r="B19" t="n">
-        <v>91335</v>
+        <v>5172</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,37 +2520,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680485</v>
+        <v>680380</v>
       </c>
       <c r="R19" t="n">
-        <v>6601135</v>
+        <v>6601066</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2595,6 +2597,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2613,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121411439</v>
+        <v>121410858</v>
       </c>
       <c r="B20" t="n">
-        <v>8424</v>
+        <v>5192</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680555</v>
+        <v>680820</v>
       </c>
       <c r="R20" t="n">
-        <v>6601112</v>
+        <v>6601031</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121410858</v>
+        <v>121414195</v>
       </c>
       <c r="B21" t="n">
-        <v>5192</v>
+        <v>95691</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,39 +2739,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680820</v>
+        <v>680470</v>
       </c>
       <c r="R21" t="n">
-        <v>6601031</v>
+        <v>6601110</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121410856</v>
+        <v>121410676</v>
       </c>
       <c r="B23" t="n">
         <v>5172</v>
@@ -2982,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680820</v>
+        <v>680680</v>
       </c>
       <c r="R23" t="n">
-        <v>6601031</v>
+        <v>6601025</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,7 +3042,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121414014</v>
+        <v>121412576</v>
       </c>
       <c r="B24" t="n">
         <v>57372</v>
@@ -3092,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680401</v>
+        <v>680490</v>
       </c>
       <c r="R24" t="n">
-        <v>6601033</v>
+        <v>6601144</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3152,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121413912</v>
+        <v>121411444</v>
       </c>
       <c r="B25" t="n">
         <v>57372</v>
@@ -3188,24 +3186,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680381</v>
+        <v>680555</v>
       </c>
       <c r="R25" t="n">
-        <v>6601114</v>
+        <v>6601110</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3264,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121414195</v>
+        <v>121412758</v>
       </c>
       <c r="B26" t="n">
-        <v>95691</v>
+        <v>8435</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3280,34 +3275,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680470</v>
+        <v>680420</v>
       </c>
       <c r="R26" t="n">
-        <v>6601110</v>
+        <v>6601183</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,6 +3352,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3366,7 +3371,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121411085</v>
+        <v>121412711</v>
       </c>
       <c r="B27" t="n">
         <v>57509</v>
@@ -3414,13 +3419,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680741</v>
+        <v>680420</v>
       </c>
       <c r="R27" t="n">
-        <v>6601120</v>
+        <v>6601183</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3476,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121411444</v>
+        <v>121414116</v>
       </c>
       <c r="B28" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3492,39 +3497,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680555</v>
+        <v>680468</v>
       </c>
       <c r="R28" t="n">
-        <v>6601110</v>
+        <v>6601091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121411500</v>
+        <v>121412767</v>
       </c>
       <c r="B29" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,43 +3595,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680512</v>
+        <v>680411</v>
       </c>
       <c r="R29" t="n">
-        <v>6601083</v>
+        <v>6601181</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,10 +3693,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121410851</v>
+        <v>121414121</v>
       </c>
       <c r="B30" t="n">
-        <v>90720</v>
+        <v>5172</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3702,38 +3705,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680816</v>
+        <v>680458</v>
       </c>
       <c r="R30" t="n">
-        <v>6601025</v>
+        <v>6601079</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3774,6 +3786,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3792,10 +3805,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121411550</v>
+        <v>121412820</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3808,34 +3821,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680577</v>
+        <v>680357</v>
       </c>
       <c r="R31" t="n">
-        <v>6601111</v>
+        <v>6601265</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,19 +3886,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,22 +3903,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121412767</v>
+        <v>121411500</v>
       </c>
       <c r="B32" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3916,46 +3927,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680411</v>
+        <v>680512</v>
       </c>
       <c r="R32" t="n">
-        <v>6601181</v>
+        <v>6601083</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,10 +4022,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121412756</v>
+        <v>121412572</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>91335</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4030,45 +4038,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680420</v>
+        <v>680485</v>
       </c>
       <c r="R33" t="n">
-        <v>6601183</v>
+        <v>6601135</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121412770</v>
+        <v>121411550</v>
       </c>
       <c r="B34" t="n">
-        <v>8424</v>
+        <v>90720</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4136,47 +4136,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680419</v>
+        <v>680577</v>
       </c>
       <c r="R34" t="n">
-        <v>6601182</v>
+        <v>6601111</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,30 +4197,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121412669</v>
+        <v>121410856</v>
       </c>
       <c r="B2" t="n">
-        <v>95691</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680434</v>
+        <v>680820</v>
       </c>
       <c r="R2" t="n">
-        <v>6601196</v>
+        <v>6601031</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121412756</v>
+        <v>121411444</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -811,24 +816,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680420</v>
+        <v>680555</v>
       </c>
       <c r="R3" t="n">
-        <v>6601183</v>
+        <v>6601110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410996</v>
+        <v>121413970</v>
       </c>
       <c r="B4" t="n">
-        <v>100371</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +905,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680804</v>
+        <v>680380</v>
       </c>
       <c r="R4" t="n">
-        <v>6601124</v>
+        <v>6601066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,6 +982,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121413912</v>
+        <v>121411550</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,42 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680381</v>
+        <v>680577</v>
       </c>
       <c r="R5" t="n">
-        <v>6601114</v>
+        <v>6601111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,9 +1074,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121412634</v>
+        <v>121412711</v>
       </c>
       <c r="B6" t="n">
-        <v>5192</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,43 +1125,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680449</v>
+        <v>680420</v>
       </c>
       <c r="R6" t="n">
-        <v>6601206</v>
+        <v>6601183</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121411439</v>
+        <v>121412680</v>
       </c>
       <c r="B7" t="n">
-        <v>8424</v>
+        <v>95691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,39 +1239,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680555</v>
+        <v>680489</v>
       </c>
       <c r="R7" t="n">
-        <v>6601112</v>
+        <v>6601147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,9 +1296,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,22 +1323,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121412678</v>
+        <v>121414195</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>95691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,39 +1351,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680425</v>
+        <v>680470</v>
       </c>
       <c r="R8" t="n">
-        <v>6601193</v>
+        <v>6601110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121412680</v>
+        <v>121414014</v>
       </c>
       <c r="B9" t="n">
-        <v>95691</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,38 +1449,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680489</v>
+        <v>680401</v>
       </c>
       <c r="R9" t="n">
-        <v>6601147</v>
+        <v>6601033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,19 +1518,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,22 +1535,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121413923</v>
+        <v>121411092</v>
       </c>
       <c r="B10" t="n">
-        <v>57247</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,16 +1563,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,24 +1581,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680385</v>
+        <v>680739</v>
       </c>
       <c r="R10" t="n">
-        <v>6601107</v>
+        <v>6601133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121412770</v>
+        <v>121414116</v>
       </c>
       <c r="B11" t="n">
-        <v>8424</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,47 +1666,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680419</v>
+        <v>680468</v>
       </c>
       <c r="R11" t="n">
-        <v>6601182</v>
+        <v>6601091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1738,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1754,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121410856</v>
+        <v>121412634</v>
       </c>
       <c r="B12" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680820</v>
+        <v>680449</v>
       </c>
       <c r="R12" t="n">
-        <v>6601031</v>
+        <v>6601206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1968,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121411085</v>
+        <v>121413912</v>
       </c>
       <c r="B14" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2006,7 +2008,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2016,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680741</v>
+        <v>680381</v>
       </c>
       <c r="R14" t="n">
-        <v>6601120</v>
+        <v>6601114</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121410851</v>
+        <v>121411085</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,37 +2096,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680816</v>
+        <v>680741</v>
       </c>
       <c r="R15" t="n">
-        <v>6601025</v>
+        <v>6601120</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121414014</v>
+        <v>121411500</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,46 +2202,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680401</v>
+        <v>680512</v>
       </c>
       <c r="R16" t="n">
-        <v>6601033</v>
+        <v>6601083</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121411191</v>
+        <v>121414121</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,43 +2309,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680709</v>
+        <v>680458</v>
       </c>
       <c r="R17" t="n">
-        <v>6601109</v>
+        <v>6601079</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,6 +2390,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2397,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121411092</v>
+        <v>121412678</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,31 +2421,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2442,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680739</v>
+        <v>680425</v>
       </c>
       <c r="R18" t="n">
-        <v>6601133</v>
+        <v>6601193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121413970</v>
+        <v>121412669</v>
       </c>
       <c r="B19" t="n">
-        <v>5172</v>
+        <v>95691</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,43 +2532,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680380</v>
+        <v>680434</v>
       </c>
       <c r="R19" t="n">
-        <v>6601066</v>
+        <v>6601196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,7 +2600,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2616,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121410858</v>
+        <v>121410996</v>
       </c>
       <c r="B20" t="n">
-        <v>5192</v>
+        <v>100371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2632,39 +2634,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680820</v>
+        <v>680804</v>
       </c>
       <c r="R20" t="n">
-        <v>6601031</v>
+        <v>6601124</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121414195</v>
+        <v>121411191</v>
       </c>
       <c r="B21" t="n">
-        <v>95691</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,38 +2732,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680470</v>
+        <v>680709</v>
       </c>
       <c r="R21" t="n">
-        <v>6601110</v>
+        <v>6601109</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121410676</v>
+        <v>121413923</v>
       </c>
       <c r="B23" t="n">
-        <v>5172</v>
+        <v>57247</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,43 +2949,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680680</v>
+        <v>680385</v>
       </c>
       <c r="R23" t="n">
-        <v>6601025</v>
+        <v>6601107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121412576</v>
+        <v>121410676</v>
       </c>
       <c r="B24" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3054,46 +3059,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680490</v>
+        <v>680680</v>
       </c>
       <c r="R24" t="n">
-        <v>6601144</v>
+        <v>6601025</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121411444</v>
+        <v>121411439</v>
       </c>
       <c r="B25" t="n">
-        <v>57372</v>
+        <v>8424</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3164,31 +3166,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3200,7 +3202,7 @@
         <v>680555</v>
       </c>
       <c r="R25" t="n">
-        <v>6601110</v>
+        <v>6601112</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,10 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121412758</v>
+        <v>121412576</v>
       </c>
       <c r="B26" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,34 +3273,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3308,10 +3309,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680420</v>
+        <v>680490</v>
       </c>
       <c r="R26" t="n">
-        <v>6601183</v>
+        <v>6601144</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,7 +3353,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121412711</v>
+        <v>121412767</v>
       </c>
       <c r="B27" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3387,21 +3387,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680420</v>
+        <v>680411</v>
       </c>
       <c r="R27" t="n">
-        <v>6601183</v>
+        <v>6601181</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121414116</v>
+        <v>121412572</v>
       </c>
       <c r="B28" t="n">
-        <v>90720</v>
+        <v>91335</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3493,25 +3493,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3521,13 +3521,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680468</v>
+        <v>680485</v>
       </c>
       <c r="R28" t="n">
-        <v>6601091</v>
+        <v>6601135</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121412767</v>
+        <v>121412770</v>
       </c>
       <c r="B29" t="n">
-        <v>57372</v>
+        <v>8424</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,33 +3595,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3631,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680411</v>
+        <v>680419</v>
       </c>
       <c r="R29" t="n">
-        <v>6601181</v>
+        <v>6601182</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,6 +3676,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3693,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121414121</v>
+        <v>121410858</v>
       </c>
       <c r="B30" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3709,43 +3711,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680458</v>
+        <v>680820</v>
       </c>
       <c r="R30" t="n">
-        <v>6601079</v>
+        <v>6601031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,7 +3784,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3805,10 +3802,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121412820</v>
+        <v>121412756</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>57725</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3817,20 +3814,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3843,7 +3840,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3850,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680357</v>
+        <v>680420</v>
       </c>
       <c r="R31" t="n">
-        <v>6601265</v>
+        <v>6601183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,10 +3912,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121411500</v>
+        <v>121412758</v>
       </c>
       <c r="B32" t="n">
-        <v>5172</v>
+        <v>8435</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3931,39 +3928,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680512</v>
+        <v>680420</v>
       </c>
       <c r="R32" t="n">
-        <v>6601083</v>
+        <v>6601183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4004,6 +4005,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4022,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121412572</v>
+        <v>121410851</v>
       </c>
       <c r="B33" t="n">
-        <v>91335</v>
+        <v>90720</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4034,25 +4036,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4062,13 +4064,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680485</v>
+        <v>680816</v>
       </c>
       <c r="R33" t="n">
-        <v>6601135</v>
+        <v>6601025</v>
       </c>
       <c r="S33" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4124,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121411550</v>
+        <v>121412820</v>
       </c>
       <c r="B34" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4140,34 +4142,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680577</v>
+        <v>680357</v>
       </c>
       <c r="R34" t="n">
-        <v>6601111</v>
+        <v>6601265</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4197,19 +4207,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4224,12 +4224,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -1970,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121413912</v>
+        <v>121411500</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,46 +1982,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680381</v>
+        <v>680512</v>
       </c>
       <c r="R14" t="n">
-        <v>6601114</v>
+        <v>6601083</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121411085</v>
+        <v>121413912</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2118,7 +2115,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2128,13 +2125,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680741</v>
+        <v>680381</v>
       </c>
       <c r="R15" t="n">
-        <v>6601120</v>
+        <v>6601114</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2190,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121411500</v>
+        <v>121411085</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>57509</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,46 +2199,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680512</v>
+        <v>680741</v>
       </c>
       <c r="R16" t="n">
-        <v>6601083</v>
+        <v>6601120</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412669</v>
+        <v>121413892</v>
       </c>
       <c r="B19" t="n">
-        <v>95691</v>
+        <v>57372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,38 +2528,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680434</v>
+        <v>680392</v>
       </c>
       <c r="R19" t="n">
-        <v>6601196</v>
+        <v>6601145</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121410996</v>
+        <v>121412669</v>
       </c>
       <c r="B20" t="n">
-        <v>100371</v>
+        <v>95691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2642,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680804</v>
+        <v>680434</v>
       </c>
       <c r="R20" t="n">
-        <v>6601124</v>
+        <v>6601196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121411191</v>
+        <v>121413923</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>57247</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,16 +2744,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2754,21 +2762,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680709</v>
+        <v>680385</v>
       </c>
       <c r="R21" t="n">
-        <v>6601109</v>
+        <v>6601107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,7 +2838,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121413892</v>
+        <v>121411191</v>
       </c>
       <c r="B22" t="n">
         <v>57372</v>
@@ -2861,24 +2872,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680392</v>
+        <v>680709</v>
       </c>
       <c r="R22" t="n">
-        <v>6601145</v>
+        <v>6601109</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121413923</v>
+        <v>121410996</v>
       </c>
       <c r="B23" t="n">
-        <v>57247</v>
+        <v>100371</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,46 +2957,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100001</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680385</v>
+        <v>680804</v>
       </c>
       <c r="R23" t="n">
-        <v>6601107</v>
+        <v>6601124</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121413892</v>
+        <v>121412669</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
+        <v>95691</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,46 +2528,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680392</v>
+        <v>680434</v>
       </c>
       <c r="R19" t="n">
-        <v>6601145</v>
+        <v>6601196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121412669</v>
+        <v>121410996</v>
       </c>
       <c r="B20" t="n">
-        <v>95691</v>
+        <v>100371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680434</v>
+        <v>680804</v>
       </c>
       <c r="R20" t="n">
-        <v>6601196</v>
+        <v>6601124</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121413923</v>
+        <v>121411191</v>
       </c>
       <c r="B21" t="n">
-        <v>57247</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,16 +2736,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2762,24 +2754,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680385</v>
+        <v>680709</v>
       </c>
       <c r="R21" t="n">
-        <v>6601107</v>
+        <v>6601109</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,7 +2827,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121411191</v>
+        <v>121413892</v>
       </c>
       <c r="B22" t="n">
         <v>57372</v>
@@ -2872,21 +2861,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680709</v>
+        <v>680392</v>
       </c>
       <c r="R22" t="n">
-        <v>6601109</v>
+        <v>6601145</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121410996</v>
+        <v>121413923</v>
       </c>
       <c r="B23" t="n">
-        <v>100371</v>
+        <v>57247</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,38 +2949,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680804</v>
+        <v>680385</v>
       </c>
       <c r="R23" t="n">
-        <v>6601124</v>
+        <v>6601107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121410856</v>
+        <v>121411550</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680820</v>
+        <v>680577</v>
       </c>
       <c r="R2" t="n">
-        <v>6601031</v>
+        <v>6601111</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,9 +748,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121411444</v>
+        <v>121411191</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680555</v>
+        <v>680709</v>
       </c>
       <c r="R3" t="n">
-        <v>6601110</v>
+        <v>6601109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121413970</v>
+        <v>121414121</v>
       </c>
       <c r="B4" t="n">
-        <v>5172</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680380</v>
+        <v>680458</v>
       </c>
       <c r="R4" t="n">
-        <v>6601066</v>
+        <v>6601079</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121411550</v>
+        <v>121411092</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680577</v>
+        <v>680739</v>
       </c>
       <c r="R5" t="n">
-        <v>6601111</v>
+        <v>6601133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,19 +1084,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121412711</v>
+        <v>121412820</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,7 +1151,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680420</v>
+        <v>680357</v>
       </c>
       <c r="R6" t="n">
-        <v>6601183</v>
+        <v>6601265</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121412680</v>
+        <v>121412758</v>
       </c>
       <c r="B7" t="n">
-        <v>95691</v>
+        <v>8436</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,34 +1239,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Issjön, Upl</t>
+          <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680489</v>
+        <v>680420</v>
       </c>
       <c r="R7" t="n">
-        <v>6601147</v>
+        <v>6601183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,49 +1305,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121414195</v>
+        <v>121410851</v>
       </c>
       <c r="B8" t="n">
-        <v>95691</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680470</v>
+        <v>680816</v>
       </c>
       <c r="R8" t="n">
-        <v>6601110</v>
+        <v>6601025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121414014</v>
+        <v>121410858</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,20 +1449,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1471,24 +1471,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680401</v>
+        <v>680820</v>
       </c>
       <c r="R9" t="n">
-        <v>6601033</v>
+        <v>6601031</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411092</v>
+        <v>121411444</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680739</v>
+        <v>680555</v>
       </c>
       <c r="R10" t="n">
-        <v>6601133</v>
+        <v>6601110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121414116</v>
+        <v>121413970</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,38 +1663,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680468</v>
+        <v>680380</v>
       </c>
       <c r="R11" t="n">
-        <v>6601091</v>
+        <v>6601066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,6 +1744,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1756,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121412634</v>
+        <v>121411500</v>
       </c>
       <c r="B12" t="n">
-        <v>5192</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680449</v>
+        <v>680512</v>
       </c>
       <c r="R12" t="n">
-        <v>6601206</v>
+        <v>6601083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,7 +1873,7 @@
         <v>121411749</v>
       </c>
       <c r="B13" t="n">
-        <v>8424</v>
+        <v>8425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121411500</v>
+        <v>121414195</v>
       </c>
       <c r="B14" t="n">
-        <v>5172</v>
+        <v>95699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,39 +1993,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680512</v>
+        <v>680470</v>
       </c>
       <c r="R14" t="n">
-        <v>6601083</v>
+        <v>6601110</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121413912</v>
+        <v>121410856</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,46 +2091,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680381</v>
+        <v>680820</v>
       </c>
       <c r="R15" t="n">
-        <v>6601114</v>
+        <v>6601031</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121411085</v>
+        <v>121412572</v>
       </c>
       <c r="B16" t="n">
-        <v>57509</v>
+        <v>91343</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,49 +2198,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680741</v>
+        <v>680485</v>
       </c>
       <c r="R16" t="n">
-        <v>6601120</v>
+        <v>6601135</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2297,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121414121</v>
+        <v>121412678</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,25 +2322,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680458</v>
+        <v>680425</v>
       </c>
       <c r="R17" t="n">
-        <v>6601079</v>
+        <v>6601193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,7 +2377,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2409,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121412678</v>
+        <v>121414014</v>
       </c>
       <c r="B18" t="n">
-        <v>5172</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,43 +2407,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680425</v>
+        <v>680401</v>
       </c>
       <c r="R18" t="n">
-        <v>6601193</v>
+        <v>6601033</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412669</v>
+        <v>121412576</v>
       </c>
       <c r="B19" t="n">
-        <v>95691</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,38 +2517,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680434</v>
+        <v>680490</v>
       </c>
       <c r="R19" t="n">
-        <v>6601196</v>
+        <v>6601144</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121410996</v>
+        <v>121412669</v>
       </c>
       <c r="B20" t="n">
-        <v>100371</v>
+        <v>95699</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680804</v>
+        <v>680434</v>
       </c>
       <c r="R20" t="n">
-        <v>6601124</v>
+        <v>6601196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121411191</v>
+        <v>121412634</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2732,20 +2729,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2756,7 +2753,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2765,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680709</v>
+        <v>680449</v>
       </c>
       <c r="R21" t="n">
-        <v>6601109</v>
+        <v>6601206</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121413892</v>
+        <v>121412770</v>
       </c>
       <c r="B22" t="n">
-        <v>57372</v>
+        <v>8425</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2839,33 +2836,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2875,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680392</v>
+        <v>680419</v>
       </c>
       <c r="R22" t="n">
-        <v>6601145</v>
+        <v>6601182</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,6 +2917,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2937,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121413923</v>
+        <v>121411085</v>
       </c>
       <c r="B23" t="n">
-        <v>57247</v>
+        <v>57510</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2975,7 +2974,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2985,13 +2984,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680385</v>
+        <v>680741</v>
       </c>
       <c r="R23" t="n">
-        <v>6601107</v>
+        <v>6601120</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3047,10 +3046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121410676</v>
+        <v>121413912</v>
       </c>
       <c r="B24" t="n">
-        <v>5172</v>
+        <v>57373</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,43 +3058,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680680</v>
+        <v>680381</v>
       </c>
       <c r="R24" t="n">
-        <v>6601025</v>
+        <v>6601114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121411439</v>
+        <v>121412756</v>
       </c>
       <c r="B25" t="n">
-        <v>8424</v>
+        <v>57726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3170,39 +3172,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680555</v>
+        <v>680420</v>
       </c>
       <c r="R25" t="n">
-        <v>6601112</v>
+        <v>6601183</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121412576</v>
+        <v>121412711</v>
       </c>
       <c r="B26" t="n">
-        <v>57372</v>
+        <v>57510</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3277,21 +3282,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3299,7 +3304,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3309,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680490</v>
+        <v>680420</v>
       </c>
       <c r="R26" t="n">
-        <v>6601144</v>
+        <v>6601183</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3371,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121412767</v>
+        <v>121413892</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680411</v>
+        <v>680392</v>
       </c>
       <c r="R27" t="n">
-        <v>6601181</v>
+        <v>6601145</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121412572</v>
+        <v>121411439</v>
       </c>
       <c r="B28" t="n">
-        <v>91335</v>
+        <v>8425</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,37 +3502,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680485</v>
+        <v>680555</v>
       </c>
       <c r="R28" t="n">
-        <v>6601135</v>
+        <v>6601112</v>
       </c>
       <c r="S28" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3583,10 +3593,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121412770</v>
+        <v>121414116</v>
       </c>
       <c r="B29" t="n">
-        <v>8424</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,47 +3605,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680419</v>
+        <v>680468</v>
       </c>
       <c r="R29" t="n">
-        <v>6601182</v>
+        <v>6601091</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3677,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121410858</v>
+        <v>121412680</v>
       </c>
       <c r="B30" t="n">
-        <v>5192</v>
+        <v>95699</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,39 +3711,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Issjön, Issjön, Upl</t>
+          <t>Issjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680820</v>
+        <v>680489</v>
       </c>
       <c r="R30" t="n">
-        <v>6601031</v>
+        <v>6601147</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,9 +3768,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3790,22 +3795,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121412756</v>
+        <v>121412767</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>57373</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3814,20 +3819,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3840,7 +3845,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3850,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680420</v>
+        <v>680411</v>
       </c>
       <c r="R31" t="n">
-        <v>6601183</v>
+        <v>6601181</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121412758</v>
+        <v>121413923</v>
       </c>
       <c r="B32" t="n">
-        <v>8435</v>
+        <v>57248</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3924,34 +3929,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3961,10 +3965,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680420</v>
+        <v>680385</v>
       </c>
       <c r="R32" t="n">
-        <v>6601183</v>
+        <v>6601107</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4009,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4024,10 +4027,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121410851</v>
+        <v>121410996</v>
       </c>
       <c r="B33" t="n">
-        <v>90720</v>
+        <v>100379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,25 +4039,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4064,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680816</v>
+        <v>680804</v>
       </c>
       <c r="R33" t="n">
-        <v>6601025</v>
+        <v>6601124</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121412820</v>
+        <v>121410676</v>
       </c>
       <c r="B34" t="n">
-        <v>57372</v>
+        <v>5173</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,46 +4141,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680357</v>
+        <v>680680</v>
       </c>
       <c r="R34" t="n">
-        <v>6601265</v>
+        <v>6601025</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
         <v>121411629</v>
       </c>
       <c r="B35" t="n">
-        <v>95691</v>
+        <v>95699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -2505,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412576</v>
+        <v>121412669</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>95699</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,46 +2517,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680490</v>
+        <v>680434</v>
       </c>
       <c r="R19" t="n">
-        <v>6601144</v>
+        <v>6601196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121412669</v>
+        <v>121412576</v>
       </c>
       <c r="B20" t="n">
-        <v>95699</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,38 +2619,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680434</v>
+        <v>680490</v>
       </c>
       <c r="R20" t="n">
-        <v>6601196</v>
+        <v>6601144</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121413892</v>
+        <v>121411439</v>
       </c>
       <c r="B27" t="n">
-        <v>57373</v>
+        <v>8425</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3388,46 +3388,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680392</v>
+        <v>680555</v>
       </c>
       <c r="R27" t="n">
-        <v>6601145</v>
+        <v>6601112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,10 +3483,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121411439</v>
+        <v>121413892</v>
       </c>
       <c r="B28" t="n">
-        <v>8425</v>
+        <v>57373</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3498,43 +3495,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680555</v>
+        <v>680392</v>
       </c>
       <c r="R28" t="n">
-        <v>6601112</v>
+        <v>6601145</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 55611-2024 artfynd.xlsx
+++ b/artfynd/A 55611-2024 artfynd.xlsx
@@ -2288,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121412678</v>
+        <v>121414014</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,43 +2300,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680425</v>
+        <v>680401</v>
       </c>
       <c r="R17" t="n">
-        <v>6601193</v>
+        <v>6601033</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121414014</v>
+        <v>121412678</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,46 +2410,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680401</v>
+        <v>680425</v>
       </c>
       <c r="R18" t="n">
-        <v>6601033</v>
+        <v>6601193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121412669</v>
+        <v>121412576</v>
       </c>
       <c r="B19" t="n">
-        <v>95699</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,38 +2517,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680434</v>
+        <v>680490</v>
       </c>
       <c r="R19" t="n">
-        <v>6601196</v>
+        <v>6601144</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121412576</v>
+        <v>121412669</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>95699</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,46 +2627,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Issjön, Issjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680490</v>
+        <v>680434</v>
       </c>
       <c r="R20" t="n">
-        <v>6601144</v>
+        <v>6601196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
